--- a/screenshots/testas.xlsx
+++ b/screenshots/testas.xlsx
@@ -103,7 +103,7 @@
       </c>
       <c r="B3" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-16 11:51</t>
+          <t xml:space="preserve">2026-08-16 11:56</t>
         </is>
       </c>
     </row>
@@ -250,17 +250,18 @@
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="46" customWidth="1"/>
-    <col min="3" max="3" width="9" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="3" max="3" width="13" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
     <col min="5" max="5" width="13" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
-    <col min="7" max="7" width="15" customWidth="1"/>
-    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="7" max="7" width="9" customWidth="1"/>
+    <col min="8" max="8" width="15" customWidth="1"/>
     <col min="9" max="9" width="12" customWidth="1"/>
     <col min="10" max="10" width="12" customWidth="1"/>
     <col min="11" max="11" width="12" customWidth="1"/>
-    <col min="12" max="12" width="10" customWidth="1"/>
-    <col min="13" max="13" width="14" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
+    <col min="13" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -290,7 +291,7 @@
       </c>
       <c r="B3" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-16 11:51</t>
+          <t xml:space="preserve">2026-08-16 11:56</t>
         </is>
       </c>
     </row>
@@ -314,12 +315,12 @@
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rodyta</t>
+          <t xml:space="preserve">Matė (sesijos)</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Įdėta</t>
+          <t xml:space="preserve">Įsidėjo (sesijos)</t>
         </is>
       </c>
       <c r="E5" s="1" t="inlineStr">
@@ -329,40 +330,45 @@
       </c>
       <c r="F5" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Įdėta vnt.</t>
+        </is>
+      </c>
+      <c r="G5" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Išimta</t>
         </is>
       </c>
-      <c r="G5" s="1" t="inlineStr">
+      <c r="H5" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Išėmimo rodiklis</t>
         </is>
       </c>
-      <c r="H5" s="1" t="inlineStr">
+      <c r="I5" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Parduota vnt.</t>
         </is>
       </c>
-      <c r="I5" s="1" t="inlineStr">
+      <c r="J5" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Pajamos</t>
         </is>
       </c>
-      <c r="J5" s="1" t="inlineStr">
+      <c r="K5" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Savikaina</t>
         </is>
       </c>
-      <c r="K5" s="1" t="inlineStr">
+      <c r="L5" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Pelnas</t>
         </is>
       </c>
-      <c r="L5" s="1" t="inlineStr">
+      <c r="M5" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Marža</t>
         </is>
       </c>
-      <c r="M5" s="1" t="inlineStr">
+      <c r="N5" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Dalis apyvartoje</t>
         </is>
@@ -378,36 +384,39 @@
         </is>
       </c>
       <c r="C6" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D6" s="2">
+        <v>3</v>
+      </c>
+      <c r="E6" s="4">
+        <v>1</v>
+      </c>
+      <c r="F6" s="2">
         <v>9</v>
       </c>
-      <c r="E6" s="4">
-        <v>2.25</v>
-      </c>
-      <c r="F6" s="2">
-        <v>1</v>
-      </c>
-      <c r="G6" s="4">
+      <c r="G6" s="2">
+        <v>1</v>
+      </c>
+      <c r="H6" s="4">
         <v>0.11111111111111</v>
       </c>
-      <c r="H6" s="2">
+      <c r="I6" s="2">
         <v>7</v>
       </c>
-      <c r="I6" s="3">
+      <c r="J6" s="3">
         <v>19.61</v>
       </c>
-      <c r="J6" s="3">
+      <c r="K6" s="3">
         <v>14.07</v>
       </c>
-      <c r="K6" s="3">
+      <c r="L6" s="3">
         <v>2.14</v>
       </c>
-      <c r="L6" s="4">
+      <c r="M6" s="4">
         <v>0.13204487506374</v>
       </c>
-      <c r="M6" s="4">
+      <c r="N6" s="4">
         <v>0.40752285951787</v>
       </c>
     </row>
@@ -421,36 +430,39 @@
         </is>
       </c>
       <c r="C7" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D7" s="2">
         <v>3</v>
       </c>
       <c r="E7" s="4">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="F7" s="2">
-        <v>0</v>
-      </c>
-      <c r="G7" s="4">
-        <v>0</v>
-      </c>
-      <c r="H7" s="2">
-        <v>1</v>
-      </c>
-      <c r="I7" s="3">
+        <v>3</v>
+      </c>
+      <c r="G7" s="2">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0</v>
+      </c>
+      <c r="I7" s="2">
+        <v>1</v>
+      </c>
+      <c r="J7" s="3">
         <v>2.97</v>
       </c>
-      <c r="J7" s="3">
+      <c r="K7" s="3">
         <v>2.01</v>
       </c>
-      <c r="K7" s="3">
+      <c r="L7" s="3">
         <v>0.44</v>
       </c>
-      <c r="L7" s="4">
+      <c r="M7" s="4">
         <v>0.17925925925926</v>
       </c>
-      <c r="M7" s="4">
+      <c r="N7" s="4">
         <v>0.061720698254364</v>
       </c>
     </row>
@@ -473,27 +485,30 @@
         <v>1</v>
       </c>
       <c r="F8" s="2">
-        <v>0</v>
-      </c>
-      <c r="G8" s="4">
-        <v>0</v>
-      </c>
-      <c r="H8" s="2">
-        <v>1</v>
-      </c>
-      <c r="I8" s="3">
+        <v>2</v>
+      </c>
+      <c r="G8" s="2">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0</v>
+      </c>
+      <c r="I8" s="2">
+        <v>1</v>
+      </c>
+      <c r="J8" s="3">
         <v>2.97</v>
       </c>
-      <c r="J8" s="3">
-        <v>0</v>
-      </c>
       <c r="K8" s="3">
+        <v>0</v>
+      </c>
+      <c r="L8" s="3">
         <v>2.45</v>
       </c>
-      <c r="L8" s="4">
+      <c r="M8" s="4">
         <v>0.99814814814815</v>
       </c>
-      <c r="M8" s="4">
+      <c r="N8" s="4">
         <v>0.061720698254364</v>
       </c>
     </row>
@@ -507,36 +522,39 @@
         </is>
       </c>
       <c r="C9" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D9" s="2">
         <v>2</v>
       </c>
       <c r="E9" s="4">
-        <v>0.5</v>
+        <v>0.66666666666667</v>
       </c>
       <c r="F9" s="2">
-        <v>0</v>
-      </c>
-      <c r="G9" s="4">
-        <v>0</v>
-      </c>
-      <c r="H9" s="2">
-        <v>1</v>
-      </c>
-      <c r="I9" s="3">
+        <v>2</v>
+      </c>
+      <c r="G9" s="2">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0</v>
+      </c>
+      <c r="I9" s="2">
+        <v>1</v>
+      </c>
+      <c r="J9" s="3">
         <v>2.88</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2.01</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>0.37</v>
       </c>
-      <c r="L9" s="4">
+      <c r="M9" s="4">
         <v>0.15545138888889</v>
       </c>
-      <c r="M9" s="4">
+      <c r="N9" s="4">
         <v>0.059850374064838</v>
       </c>
     </row>
@@ -550,36 +568,39 @@
         </is>
       </c>
       <c r="C10" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D10" s="2">
         <v>3</v>
       </c>
       <c r="E10" s="4">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="F10" s="2">
-        <v>0</v>
-      </c>
-      <c r="G10" s="4">
-        <v>0</v>
-      </c>
-      <c r="H10" s="2">
-        <v>1</v>
-      </c>
-      <c r="I10" s="3">
+        <v>3</v>
+      </c>
+      <c r="G10" s="2">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0</v>
+      </c>
+      <c r="I10" s="2">
+        <v>1</v>
+      </c>
+      <c r="J10" s="3">
         <v>2.88</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2.01</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>0.37</v>
       </c>
-      <c r="L10" s="4">
+      <c r="M10" s="4">
         <v>0.15545138888889</v>
       </c>
-      <c r="M10" s="4">
+      <c r="N10" s="4">
         <v>0.059850374064838</v>
       </c>
     </row>
@@ -602,27 +623,30 @@
         <v>1</v>
       </c>
       <c r="F11" s="2">
-        <v>0</v>
-      </c>
-      <c r="G11" s="4">
-        <v>0</v>
-      </c>
-      <c r="H11" s="2">
-        <v>1</v>
-      </c>
-      <c r="I11" s="3">
+        <v>2</v>
+      </c>
+      <c r="G11" s="2">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4">
+        <v>0</v>
+      </c>
+      <c r="I11" s="2">
+        <v>1</v>
+      </c>
+      <c r="J11" s="3">
         <v>2.85</v>
       </c>
-      <c r="J11" s="3">
+      <c r="K11" s="3">
         <v>2.01</v>
       </c>
-      <c r="K11" s="3">
+      <c r="L11" s="3">
         <v>0.35</v>
       </c>
-      <c r="L11" s="4">
+      <c r="M11" s="4">
         <v>0.14859649122807</v>
       </c>
-      <c r="M11" s="4">
+      <c r="N11" s="4">
         <v>0.059226932668329</v>
       </c>
     </row>
@@ -636,36 +660,39 @@
         </is>
       </c>
       <c r="C12" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D12" s="2">
         <v>2</v>
       </c>
       <c r="E12" s="4">
-        <v>0.5</v>
+        <v>0.66666666666667</v>
       </c>
       <c r="F12" s="2">
-        <v>0</v>
-      </c>
-      <c r="G12" s="4">
-        <v>0</v>
-      </c>
-      <c r="H12" s="2">
-        <v>1</v>
-      </c>
-      <c r="I12" s="3">
+        <v>2</v>
+      </c>
+      <c r="G12" s="2">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4">
+        <v>0</v>
+      </c>
+      <c r="I12" s="2">
+        <v>1</v>
+      </c>
+      <c r="J12" s="3">
         <v>2.85</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>2.01</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>0.35</v>
       </c>
-      <c r="L12" s="4">
+      <c r="M12" s="4">
         <v>0.14859649122807</v>
       </c>
-      <c r="M12" s="4">
+      <c r="N12" s="4">
         <v>0.059226932668329</v>
       </c>
     </row>
@@ -679,36 +706,39 @@
         </is>
       </c>
       <c r="C13" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D13" s="2">
         <v>2</v>
       </c>
       <c r="E13" s="4">
-        <v>0.5</v>
+        <v>0.66666666666667</v>
       </c>
       <c r="F13" s="2">
-        <v>0</v>
-      </c>
-      <c r="G13" s="4">
-        <v>0</v>
-      </c>
-      <c r="H13" s="2">
-        <v>1</v>
-      </c>
-      <c r="I13" s="3">
+        <v>2</v>
+      </c>
+      <c r="G13" s="2">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0</v>
+      </c>
+      <c r="I13" s="2">
+        <v>1</v>
+      </c>
+      <c r="J13" s="3">
         <v>2.8</v>
       </c>
-      <c r="J13" s="3">
+      <c r="K13" s="3">
         <v>2.01</v>
       </c>
-      <c r="K13" s="3">
+      <c r="L13" s="3">
         <v>0.3</v>
       </c>
-      <c r="L13" s="4">
+      <c r="M13" s="4">
         <v>0.12964285714286</v>
       </c>
-      <c r="M13" s="4">
+      <c r="N13" s="4">
         <v>0.058187863674148</v>
       </c>
     </row>
@@ -731,27 +761,30 @@
         <v>1</v>
       </c>
       <c r="F14" s="2">
-        <v>0</v>
-      </c>
-      <c r="G14" s="4">
-        <v>0</v>
-      </c>
-      <c r="H14" s="2">
-        <v>1</v>
-      </c>
-      <c r="I14" s="3">
+        <v>2</v>
+      </c>
+      <c r="G14" s="2">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
+        <v>0</v>
+      </c>
+      <c r="I14" s="2">
+        <v>1</v>
+      </c>
+      <c r="J14" s="3">
         <v>2.77</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>2.01</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>0.28</v>
       </c>
-      <c r="L14" s="4">
+      <c r="M14" s="4">
         <v>0.12231046931408</v>
       </c>
-      <c r="M14" s="4">
+      <c r="N14" s="4">
         <v>0.057564422277639</v>
       </c>
     </row>
@@ -765,36 +798,39 @@
         </is>
       </c>
       <c r="C15" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D15" s="2">
         <v>2</v>
       </c>
       <c r="E15" s="4">
-        <v>0.5</v>
+        <v>0.66666666666667</v>
       </c>
       <c r="F15" s="2">
-        <v>0</v>
-      </c>
-      <c r="G15" s="4">
-        <v>0</v>
-      </c>
-      <c r="H15" s="2">
-        <v>1</v>
-      </c>
-      <c r="I15" s="3">
+        <v>2</v>
+      </c>
+      <c r="G15" s="2">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0</v>
+      </c>
+      <c r="I15" s="2">
+        <v>1</v>
+      </c>
+      <c r="J15" s="3">
         <v>2.77</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>2.01</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>0.28</v>
       </c>
-      <c r="L15" s="4">
+      <c r="M15" s="4">
         <v>0.12231046931408</v>
       </c>
-      <c r="M15" s="4">
+      <c r="N15" s="4">
         <v>0.057564422277639</v>
       </c>
     </row>
@@ -808,36 +844,39 @@
         </is>
       </c>
       <c r="C16" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D16" s="2">
         <v>3</v>
       </c>
       <c r="E16" s="4">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="F16" s="2">
-        <v>0</v>
-      </c>
-      <c r="G16" s="4">
-        <v>0</v>
-      </c>
-      <c r="H16" s="2">
-        <v>1</v>
-      </c>
-      <c r="I16" s="3">
+        <v>3</v>
+      </c>
+      <c r="G16" s="2">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0</v>
+      </c>
+      <c r="I16" s="2">
+        <v>1</v>
+      </c>
+      <c r="J16" s="3">
         <v>2.77</v>
       </c>
-      <c r="J16" s="3">
+      <c r="K16" s="3">
         <v>2.01</v>
       </c>
-      <c r="K16" s="3">
+      <c r="L16" s="3">
         <v>0.28</v>
       </c>
-      <c r="L16" s="4">
+      <c r="M16" s="4">
         <v>0.12231046931408</v>
       </c>
-      <c r="M16" s="4">
+      <c r="N16" s="4">
         <v>0.057564422277639</v>
       </c>
     </row>
@@ -889,7 +928,7 @@
       </c>
       <c r="B3" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-16 11:51</t>
+          <t xml:space="preserve">2026-08-16 11:56</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1076,7 @@
       </c>
       <c r="B3" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-16 11:51</t>
+          <t xml:space="preserve">2026-08-16 11:56</t>
         </is>
       </c>
     </row>

--- a/screenshots/testas.xlsx
+++ b/screenshots/testas.xlsx
@@ -71,6 +71,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -103,7 +105,7 @@
       </c>
       <c r="B3" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-16 11:56</t>
+          <t xml:space="preserve">2026-08-16 12:31</t>
         </is>
       </c>
     </row>
@@ -132,7 +134,7 @@
           <t xml:space="preserve">Pajamos su PVM</t>
         </is>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="3" t="n">
         <v>48.12</v>
       </c>
     </row>
@@ -142,7 +144,7 @@
           <t xml:space="preserve">Pelnas</t>
         </is>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="3" t="n">
         <v>4.49</v>
       </c>
     </row>
@@ -152,8 +154,8 @@
           <t xml:space="preserve">Marža</t>
         </is>
       </c>
-      <c r="B8" s="4">
-        <v>0.1203300110742</v>
+      <c r="B8" s="4" t="n">
+        <v>0.12033</v>
       </c>
     </row>
     <row r="9">
@@ -162,7 +164,7 @@
           <t xml:space="preserve">Užsakymai su dėže</t>
         </is>
       </c>
-      <c r="B9" s="2">
+      <c r="B9" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -172,7 +174,7 @@
           <t xml:space="preserve">Vid. čekis</t>
         </is>
       </c>
-      <c r="B10" s="3">
+      <c r="B10" s="3" t="n">
         <v>48.12</v>
       </c>
     </row>
@@ -182,7 +184,7 @@
           <t xml:space="preserve">Vid. dydis (vnt.)</t>
         </is>
       </c>
-      <c r="B11" s="2">
+      <c r="B11" s="2" t="n">
         <v>17</v>
       </c>
     </row>
@@ -192,7 +194,7 @@
           <t xml:space="preserve">Parduota vnt. viso</t>
         </is>
       </c>
-      <c r="B12" s="2">
+      <c r="B12" s="2" t="n">
         <v>17</v>
       </c>
     </row>
@@ -202,7 +204,7 @@
           <t xml:space="preserve">Grąžinta</t>
         </is>
       </c>
-      <c r="B13" s="3">
+      <c r="B13" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -212,7 +214,7 @@
           <t xml:space="preserve">Dovanų savikaina</t>
         </is>
       </c>
-      <c r="B14" s="3">
+      <c r="B14" s="3" t="n">
         <v>0.66</v>
       </c>
     </row>
@@ -222,7 +224,7 @@
           <t xml:space="preserve">Eilutės be savikainos</t>
         </is>
       </c>
-      <c r="B15" s="2">
+      <c r="B15" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -241,12 +243,14 @@
       </c>
     </row>
   </sheetData>
-  <sheetViews/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:N16"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="46" customWidth="1"/>
@@ -291,7 +295,7 @@
       </c>
       <c r="B3" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-16 11:56</t>
+          <t xml:space="preserve">2026-08-16 12:31</t>
         </is>
       </c>
     </row>
@@ -375,7 +379,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2">
+      <c r="A6" s="2" t="n">
         <v>19570</v>
       </c>
       <c r="B6" s="0" t="inlineStr">
@@ -383,45 +387,45 @@
           <t xml:space="preserve">Animonda GranCarno Adult Beef: konservai šunims su šviežia jautiena, 800 g</t>
         </is>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E6" s="4">
-        <v>1</v>
-      </c>
-      <c r="F6" s="2">
+      <c r="E6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="G6" s="2">
-        <v>1</v>
-      </c>
-      <c r="H6" s="4">
-        <v>0.11111111111111</v>
-      </c>
-      <c r="I6" s="2">
+      <c r="G6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>0.111111</v>
+      </c>
+      <c r="I6" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J6" s="3">
+      <c r="J6" s="3" t="n">
         <v>19.61</v>
       </c>
-      <c r="K6" s="3">
+      <c r="K6" s="3" t="n">
         <v>14.07</v>
       </c>
-      <c r="L6" s="3">
+      <c r="L6" s="3" t="n">
         <v>2.14</v>
       </c>
-      <c r="M6" s="4">
-        <v>0.13204487506374</v>
-      </c>
-      <c r="N6" s="4">
-        <v>0.40752285951787</v>
+      <c r="M6" s="4" t="n">
+        <v>0.132045</v>
+      </c>
+      <c r="N6" s="4" t="n">
+        <v>0.407523</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2">
+      <c r="A7" s="2" t="n">
         <v>19582</v>
       </c>
       <c r="B7" s="0" t="inlineStr">
@@ -429,45 +433,45 @@
           <t xml:space="preserve">Animonda GranCarno Adult Beef + Lamb: konserv</t>
         </is>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E7" s="4">
-        <v>1</v>
-      </c>
-      <c r="F7" s="2">
+      <c r="E7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="G7" s="2">
-        <v>0</v>
-      </c>
-      <c r="H7" s="4">
-        <v>0</v>
-      </c>
-      <c r="I7" s="2">
-        <v>1</v>
-      </c>
-      <c r="J7" s="3">
+      <c r="G7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="3" t="n">
         <v>2.97</v>
       </c>
-      <c r="K7" s="3">
+      <c r="K7" s="3" t="n">
         <v>2.01</v>
       </c>
-      <c r="L7" s="3">
+      <c r="L7" s="3" t="n">
         <v>0.44</v>
       </c>
-      <c r="M7" s="4">
-        <v>0.17925925925926</v>
-      </c>
-      <c r="N7" s="4">
-        <v>0.061720698254364</v>
+      <c r="M7" s="4" t="n">
+        <v>0.179259</v>
+      </c>
+      <c r="N7" s="4" t="n">
+        <v>0.061721</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2">
+      <c r="A8" s="2" t="n">
         <v>19538</v>
       </c>
       <c r="B8" s="0" t="inlineStr">
@@ -475,45 +479,45 @@
           <t xml:space="preserve">Animonda GranCarno Adult Rumen: konservai suaugusiems šunims su galvijų prieskrandžiais, 800 g</t>
         </is>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E8" s="4">
-        <v>1</v>
-      </c>
-      <c r="F8" s="2">
+      <c r="E8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="G8" s="2">
-        <v>0</v>
-      </c>
-      <c r="H8" s="4">
-        <v>0</v>
-      </c>
-      <c r="I8" s="2">
-        <v>1</v>
-      </c>
-      <c r="J8" s="3">
+      <c r="G8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" s="3" t="n">
         <v>2.97</v>
       </c>
-      <c r="K8" s="3">
-        <v>0</v>
-      </c>
-      <c r="L8" s="3">
+      <c r="K8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="3" t="n">
         <v>2.45</v>
       </c>
-      <c r="M8" s="4">
-        <v>0.99814814814815</v>
-      </c>
-      <c r="N8" s="4">
-        <v>0.061720698254364</v>
+      <c r="M8" s="4" t="n">
+        <v>0.998148</v>
+      </c>
+      <c r="N8" s="4" t="n">
+        <v>0.061721</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2">
+      <c r="A9" s="2" t="n">
         <v>19578</v>
       </c>
       <c r="B9" s="0" t="inlineStr">
@@ -521,45 +525,45 @@
           <t xml:space="preserve">Animonda GranCarno Adult Beef + Rabbit with Herbs: konservai suaugusiems šunims su šviežia jautiena ir triušiena, paskaninta žolelėmis, 800 g</t>
         </is>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E9" s="4">
-        <v>0.66666666666667</v>
-      </c>
-      <c r="F9" s="2">
+      <c r="E9" s="4" t="n">
+        <v>0.666667</v>
+      </c>
+      <c r="F9" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="G9" s="2">
-        <v>0</v>
-      </c>
-      <c r="H9" s="4">
-        <v>0</v>
-      </c>
-      <c r="I9" s="2">
-        <v>1</v>
-      </c>
-      <c r="J9" s="3">
+      <c r="G9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" s="3" t="n">
         <v>2.88</v>
       </c>
-      <c r="K9" s="3">
+      <c r="K9" s="3" t="n">
         <v>2.01</v>
       </c>
-      <c r="L9" s="3">
+      <c r="L9" s="3" t="n">
         <v>0.37</v>
       </c>
-      <c r="M9" s="4">
-        <v>0.15545138888889</v>
-      </c>
-      <c r="N9" s="4">
-        <v>0.059850374064838</v>
+      <c r="M9" s="4" t="n">
+        <v>0.155451</v>
+      </c>
+      <c r="N9" s="4" t="n">
+        <v>0.05985</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2">
+      <c r="A10" s="2" t="n">
         <v>19562</v>
       </c>
       <c r="B10" s="0" t="inlineStr">
@@ -567,45 +571,45 @@
           <t xml:space="preserve">Animonda GranCarno Adult Duck: konservai suaugusiems šunims su šviežia antiena, 800 g</t>
         </is>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D10" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E10" s="4">
-        <v>1</v>
-      </c>
-      <c r="F10" s="2">
+      <c r="E10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="G10" s="2">
-        <v>0</v>
-      </c>
-      <c r="H10" s="4">
-        <v>0</v>
-      </c>
-      <c r="I10" s="2">
-        <v>1</v>
-      </c>
-      <c r="J10" s="3">
+      <c r="G10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="3" t="n">
         <v>2.88</v>
       </c>
-      <c r="K10" s="3">
+      <c r="K10" s="3" t="n">
         <v>2.01</v>
       </c>
-      <c r="L10" s="3">
+      <c r="L10" s="3" t="n">
         <v>0.37</v>
       </c>
-      <c r="M10" s="4">
-        <v>0.15545138888889</v>
-      </c>
-      <c r="N10" s="4">
-        <v>0.059850374064838</v>
+      <c r="M10" s="4" t="n">
+        <v>0.155451</v>
+      </c>
+      <c r="N10" s="4" t="n">
+        <v>0.05985</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2">
+      <c r="A11" s="2" t="n">
         <v>19479</v>
       </c>
       <c r="B11" s="0" t="inlineStr">
@@ -613,45 +617,45 @@
           <t xml:space="preserve">Animonda GranCarno Adult: konservai šunims su lašiša, praturtinta špinatais, 800 g</t>
         </is>
       </c>
-      <c r="C11" s="2">
+      <c r="C11" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D11" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E11" s="4">
-        <v>1</v>
-      </c>
-      <c r="F11" s="2">
+      <c r="E11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="G11" s="2">
-        <v>0</v>
-      </c>
-      <c r="H11" s="4">
-        <v>0</v>
-      </c>
-      <c r="I11" s="2">
-        <v>1</v>
-      </c>
-      <c r="J11" s="3">
+      <c r="G11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" s="3" t="n">
         <v>2.85</v>
       </c>
-      <c r="K11" s="3">
+      <c r="K11" s="3" t="n">
         <v>2.01</v>
       </c>
-      <c r="L11" s="3">
+      <c r="L11" s="3" t="n">
         <v>0.35</v>
       </c>
-      <c r="M11" s="4">
-        <v>0.14859649122807</v>
-      </c>
-      <c r="N11" s="4">
-        <v>0.059226932668329</v>
+      <c r="M11" s="4" t="n">
+        <v>0.148596</v>
+      </c>
+      <c r="N11" s="4" t="n">
+        <v>0.059227</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2">
+      <c r="A12" s="2" t="n">
         <v>19496</v>
       </c>
       <c r="B12" s="0" t="inlineStr">
@@ -659,45 +663,45 @@
           <t xml:space="preserve">Animonda GranCarno Adult: konservai suaugusiems šunims su žvėriena, 800 g</t>
         </is>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D12" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E12" s="4">
-        <v>0.66666666666667</v>
-      </c>
-      <c r="F12" s="2">
+      <c r="E12" s="4" t="n">
+        <v>0.666667</v>
+      </c>
+      <c r="F12" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="G12" s="2">
-        <v>0</v>
-      </c>
-      <c r="H12" s="4">
-        <v>0</v>
-      </c>
-      <c r="I12" s="2">
-        <v>1</v>
-      </c>
-      <c r="J12" s="3">
+      <c r="G12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" s="3" t="n">
         <v>2.85</v>
       </c>
-      <c r="K12" s="3">
+      <c r="K12" s="3" t="n">
         <v>2.01</v>
       </c>
-      <c r="L12" s="3">
+      <c r="L12" s="3" t="n">
         <v>0.35</v>
       </c>
-      <c r="M12" s="4">
-        <v>0.14859649122807</v>
-      </c>
-      <c r="N12" s="4">
-        <v>0.059226932668329</v>
+      <c r="M12" s="4" t="n">
+        <v>0.148596</v>
+      </c>
+      <c r="N12" s="4" t="n">
+        <v>0.059227</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2">
+      <c r="A13" s="2" t="n">
         <v>19504</v>
       </c>
       <c r="B13" s="0" t="inlineStr">
@@ -705,45 +709,45 @@
           <t xml:space="preserve">Animonda GranCarno Adult: konservai suaugusiems šunims su kalakutiena, 800 g</t>
         </is>
       </c>
-      <c r="C13" s="2">
+      <c r="C13" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E13" s="4">
-        <v>0.66666666666667</v>
-      </c>
-      <c r="F13" s="2">
+      <c r="E13" s="4" t="n">
+        <v>0.666667</v>
+      </c>
+      <c r="F13" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="G13" s="2">
-        <v>0</v>
-      </c>
-      <c r="H13" s="4">
-        <v>0</v>
-      </c>
-      <c r="I13" s="2">
-        <v>1</v>
-      </c>
-      <c r="J13" s="3">
+      <c r="G13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="K13" s="3">
+      <c r="K13" s="3" t="n">
         <v>2.01</v>
       </c>
-      <c r="L13" s="3">
+      <c r="L13" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="M13" s="4">
-        <v>0.12964285714286</v>
-      </c>
-      <c r="N13" s="4">
-        <v>0.058187863674148</v>
+      <c r="M13" s="4" t="n">
+        <v>0.129643</v>
+      </c>
+      <c r="N13" s="4" t="n">
+        <v>0.058188</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2">
+      <c r="A14" s="2" t="n">
         <v>19471</v>
       </c>
       <c r="B14" s="0" t="inlineStr">
@@ -751,45 +755,45 @@
           <t xml:space="preserve">Animonda GranCarno Adult: konservai šunims su širdimis, 800 g</t>
         </is>
       </c>
-      <c r="C14" s="2">
+      <c r="C14" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D14" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E14" s="4">
-        <v>1</v>
-      </c>
-      <c r="F14" s="2">
+      <c r="E14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="G14" s="2">
-        <v>0</v>
-      </c>
-      <c r="H14" s="4">
-        <v>0</v>
-      </c>
-      <c r="I14" s="2">
-        <v>1</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="G14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" s="3" t="n">
         <v>2.77</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="n">
         <v>2.01</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="n">
         <v>0.28</v>
       </c>
-      <c r="M14" s="4">
-        <v>0.12231046931408</v>
-      </c>
-      <c r="N14" s="4">
-        <v>0.057564422277639</v>
+      <c r="M14" s="4" t="n">
+        <v>0.12231</v>
+      </c>
+      <c r="N14" s="4" t="n">
+        <v>0.057564</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2">
+      <c r="A15" s="2" t="n">
         <v>19488</v>
       </c>
       <c r="B15" s="0" t="inlineStr">
@@ -797,45 +801,45 @@
           <t xml:space="preserve">Animonda GranCarno Adult: konservai šunims su elniena, pagardinta obuoliais, 800 g</t>
         </is>
       </c>
-      <c r="C15" s="2">
+      <c r="C15" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D15" s="2">
+      <c r="D15" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E15" s="4">
-        <v>0.66666666666667</v>
-      </c>
-      <c r="F15" s="2">
+      <c r="E15" s="4" t="n">
+        <v>0.666667</v>
+      </c>
+      <c r="F15" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="G15" s="2">
-        <v>0</v>
-      </c>
-      <c r="H15" s="4">
-        <v>0</v>
-      </c>
-      <c r="I15" s="2">
-        <v>1</v>
-      </c>
-      <c r="J15" s="3">
+      <c r="G15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" s="3" t="n">
         <v>2.77</v>
       </c>
-      <c r="K15" s="3">
+      <c r="K15" s="3" t="n">
         <v>2.01</v>
       </c>
-      <c r="L15" s="3">
+      <c r="L15" s="3" t="n">
         <v>0.28</v>
       </c>
-      <c r="M15" s="4">
-        <v>0.12231046931408</v>
-      </c>
-      <c r="N15" s="4">
-        <v>0.057564422277639</v>
+      <c r="M15" s="4" t="n">
+        <v>0.12231</v>
+      </c>
+      <c r="N15" s="4" t="n">
+        <v>0.057564</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2">
+      <c r="A16" s="2" t="n">
         <v>19590</v>
       </c>
       <c r="B16" s="0" t="inlineStr">
@@ -843,50 +847,52 @@
           <t xml:space="preserve">Animonda GranCarno Adult Beef + Duck Hearts: konservai suaugusiems šunims su jautiena ir ančių širdelėmis, 800 g</t>
         </is>
       </c>
-      <c r="C16" s="2">
+      <c r="C16" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D16" s="2">
+      <c r="D16" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E16" s="4">
-        <v>1</v>
-      </c>
-      <c r="F16" s="2">
+      <c r="E16" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="G16" s="2">
-        <v>0</v>
-      </c>
-      <c r="H16" s="4">
-        <v>0</v>
-      </c>
-      <c r="I16" s="2">
-        <v>1</v>
-      </c>
-      <c r="J16" s="3">
+      <c r="G16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" s="3" t="n">
         <v>2.77</v>
       </c>
-      <c r="K16" s="3">
+      <c r="K16" s="3" t="n">
         <v>2.01</v>
       </c>
-      <c r="L16" s="3">
+      <c r="L16" s="3" t="n">
         <v>0.28</v>
       </c>
-      <c r="M16" s="4">
-        <v>0.12231046931408</v>
-      </c>
-      <c r="N16" s="4">
-        <v>0.057564422277639</v>
+      <c r="M16" s="4" t="n">
+        <v>0.12231</v>
+      </c>
+      <c r="N16" s="4" t="n">
+        <v>0.057564</v>
       </c>
     </row>
   </sheetData>
-  <sheetViews/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
@@ -928,7 +934,7 @@
       </c>
       <c r="B3" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-16 11:56</t>
+          <t xml:space="preserve">2026-08-16 12:31</t>
         </is>
       </c>
     </row>
@@ -997,7 +1003,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2">
+      <c r="A6" s="2" t="n">
         <v>34942</v>
       </c>
       <c r="B6" s="0" t="inlineStr">
@@ -1010,38 +1016,40 @@
           <t xml:space="preserve">800 g</t>
         </is>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E6" s="2">
-        <v>0</v>
-      </c>
-      <c r="F6" s="4">
-        <v>0</v>
-      </c>
-      <c r="G6" s="2">
-        <v>1</v>
-      </c>
-      <c r="H6" s="2">
+      <c r="E6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="I6" s="3">
+      <c r="I6" s="3" t="n">
         <v>48.12</v>
       </c>
-      <c r="J6" s="3">
+      <c r="J6" s="3" t="n">
         <v>4.49</v>
       </c>
-      <c r="K6" s="4">
-        <v>0.1203300110742</v>
+      <c r="K6" s="4" t="n">
+        <v>0.12033</v>
       </c>
     </row>
   </sheetData>
-  <sheetViews/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
@@ -1076,7 +1084,7 @@
       </c>
       <c r="B3" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-16 11:56</t>
+          <t xml:space="preserve">2026-08-16 12:31</t>
         </is>
       </c>
     </row>
@@ -1115,11 +1123,11 @@
           <t xml:space="preserve">Atidarė dėžę</t>
         </is>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="4"/>
-      <c r="D6" s="4">
+      <c r="D6" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1129,13 +1137,13 @@
           <t xml:space="preserve">Prisidėjo bent vieną</t>
         </is>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="4" t="n">
         <v>0.75</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="4" t="n">
         <v>0.75</v>
       </c>
     </row>
@@ -1145,13 +1153,13 @@
           <t xml:space="preserve">Pasiekė minimumą</t>
         </is>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C8" s="4">
-        <v>0.66666666666667</v>
-      </c>
-      <c r="D8" s="4">
+      <c r="C8" s="4" t="n">
+        <v>0.666667</v>
+      </c>
+      <c r="D8" s="4" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -1161,13 +1169,13 @@
           <t xml:space="preserve">Įsidėjo į krepšelį</t>
         </is>
       </c>
-      <c r="B9" s="2">
-        <v>1</v>
-      </c>
-      <c r="C9" s="4">
+      <c r="B9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="4" t="n">
         <v>0.5</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D9" s="4" t="n">
         <v>0.25</v>
       </c>
     </row>
@@ -1177,23 +1185,25 @@
           <t xml:space="preserve">Nupirko</t>
         </is>
       </c>
-      <c r="B10" s="2">
-        <v>0</v>
-      </c>
-      <c r="C10" s="4">
-        <v>0</v>
-      </c>
-      <c r="D10" s="4">
+      <c r="B10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="4" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <sheetViews/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:N59"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -1299,7 +1309,7 @@
           <t xml:space="preserve">parduota</t>
         </is>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="2" t="n">
         <v>34942</v>
       </c>
       <c r="E2" s="0" t="inlineStr">
@@ -1328,16 +1338,16 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K2" s="2">
-        <v>1</v>
-      </c>
-      <c r="L2" s="2">
-        <v>0</v>
-      </c>
-      <c r="M2" s="3">
+      <c r="K2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" s="3" t="n">
         <v>48.12</v>
       </c>
-      <c r="N2" s="3">
+      <c r="N2" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1357,7 +1367,7 @@
           <t xml:space="preserve">parduota</t>
         </is>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="2" t="n">
         <v>34942</v>
       </c>
       <c r="E3" s="0" t="inlineStr">
@@ -1365,7 +1375,7 @@
           <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
         </is>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="2" t="n">
         <v>19471</v>
       </c>
       <c r="G3" s="0" t="inlineStr">
@@ -1388,16 +1398,16 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K3" s="2">
-        <v>1</v>
-      </c>
-      <c r="L3" s="2">
-        <v>0</v>
-      </c>
-      <c r="M3" s="3">
+      <c r="K3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="3" t="n">
         <v>2.77</v>
       </c>
-      <c r="N3" s="3">
+      <c r="N3" s="3" t="n">
         <v>2.01</v>
       </c>
     </row>
@@ -1417,7 +1427,7 @@
           <t xml:space="preserve">be_sav_suma</t>
         </is>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="2" t="n">
         <v>34942</v>
       </c>
       <c r="E4" s="0" t="inlineStr">
@@ -1425,7 +1435,7 @@
           <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
         </is>
       </c>
-      <c r="F4" s="2">
+      <c r="F4" s="2" t="n">
         <v>19538</v>
       </c>
       <c r="G4" s="0" t="inlineStr">
@@ -1448,16 +1458,16 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K4" s="2">
-        <v>1</v>
-      </c>
-      <c r="L4" s="2">
-        <v>0</v>
-      </c>
-      <c r="M4" s="3">
+      <c r="K4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="3" t="n">
         <v>2.97</v>
       </c>
-      <c r="N4" s="3">
+      <c r="N4" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1477,7 +1487,7 @@
           <t xml:space="preserve">be_savikainos</t>
         </is>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="2" t="n">
         <v>34942</v>
       </c>
       <c r="E5" s="0" t="inlineStr">
@@ -1485,7 +1495,7 @@
           <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
         </is>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="2" t="n">
         <v>19538</v>
       </c>
       <c r="G5" s="0" t="inlineStr">
@@ -1508,16 +1518,16 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K5" s="2">
-        <v>1</v>
-      </c>
-      <c r="L5" s="2">
-        <v>0</v>
-      </c>
-      <c r="M5" s="3">
-        <v>0</v>
-      </c>
-      <c r="N5" s="3">
+      <c r="K5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1537,7 +1547,7 @@
           <t xml:space="preserve">parduota</t>
         </is>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="2" t="n">
         <v>34942</v>
       </c>
       <c r="E6" s="0" t="inlineStr">
@@ -1545,7 +1555,7 @@
           <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
         </is>
       </c>
-      <c r="F6" s="2">
+      <c r="F6" s="2" t="n">
         <v>19538</v>
       </c>
       <c r="G6" s="0" t="inlineStr">
@@ -1568,16 +1578,16 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K6" s="2">
-        <v>1</v>
-      </c>
-      <c r="L6" s="2">
-        <v>0</v>
-      </c>
-      <c r="M6" s="3">
+      <c r="K6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="3" t="n">
         <v>2.97</v>
       </c>
-      <c r="N6" s="3">
+      <c r="N6" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1597,7 +1607,7 @@
           <t xml:space="preserve">parduota</t>
         </is>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="2" t="n">
         <v>34942</v>
       </c>
       <c r="E7" s="0" t="inlineStr">
@@ -1605,7 +1615,7 @@
           <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
         </is>
       </c>
-      <c r="F7" s="2">
+      <c r="F7" s="2" t="n">
         <v>19479</v>
       </c>
       <c r="G7" s="0" t="inlineStr">
@@ -1628,16 +1638,16 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K7" s="2">
-        <v>1</v>
-      </c>
-      <c r="L7" s="2">
-        <v>0</v>
-      </c>
-      <c r="M7" s="3">
+      <c r="K7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="3" t="n">
         <v>2.85</v>
       </c>
-      <c r="N7" s="3">
+      <c r="N7" s="3" t="n">
         <v>2.01</v>
       </c>
     </row>
@@ -1657,7 +1667,7 @@
           <t xml:space="preserve">parduota</t>
         </is>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="2" t="n">
         <v>34942</v>
       </c>
       <c r="E8" s="0" t="inlineStr">
@@ -1665,7 +1675,7 @@
           <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
         </is>
       </c>
-      <c r="F8" s="2">
+      <c r="F8" s="2" t="n">
         <v>19488</v>
       </c>
       <c r="G8" s="0" t="inlineStr">
@@ -1688,16 +1698,16 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K8" s="2">
-        <v>1</v>
-      </c>
-      <c r="L8" s="2">
-        <v>0</v>
-      </c>
-      <c r="M8" s="3">
+      <c r="K8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="3" t="n">
         <v>2.77</v>
       </c>
-      <c r="N8" s="3">
+      <c r="N8" s="3" t="n">
         <v>2.01</v>
       </c>
     </row>
@@ -1717,7 +1727,7 @@
           <t xml:space="preserve">parduota</t>
         </is>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="2" t="n">
         <v>34942</v>
       </c>
       <c r="E9" s="0" t="inlineStr">
@@ -1725,7 +1735,7 @@
           <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
         </is>
       </c>
-      <c r="F9" s="2">
+      <c r="F9" s="2" t="n">
         <v>19496</v>
       </c>
       <c r="G9" s="0" t="inlineStr">
@@ -1748,16 +1758,16 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K9" s="2">
-        <v>1</v>
-      </c>
-      <c r="L9" s="2">
-        <v>0</v>
-      </c>
-      <c r="M9" s="3">
+      <c r="K9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="3" t="n">
         <v>2.85</v>
       </c>
-      <c r="N9" s="3">
+      <c r="N9" s="3" t="n">
         <v>2.01</v>
       </c>
     </row>
@@ -1777,7 +1787,7 @@
           <t xml:space="preserve">parduota</t>
         </is>
       </c>
-      <c r="D10" s="2">
+      <c r="D10" s="2" t="n">
         <v>34942</v>
       </c>
       <c r="E10" s="0" t="inlineStr">
@@ -1785,7 +1795,7 @@
           <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
         </is>
       </c>
-      <c r="F10" s="2">
+      <c r="F10" s="2" t="n">
         <v>19504</v>
       </c>
       <c r="G10" s="0" t="inlineStr">
@@ -1808,16 +1818,16 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K10" s="2">
-        <v>1</v>
-      </c>
-      <c r="L10" s="2">
-        <v>0</v>
-      </c>
-      <c r="M10" s="3">
+      <c r="K10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="N10" s="3">
+      <c r="N10" s="3" t="n">
         <v>2.01</v>
       </c>
     </row>
@@ -1837,7 +1847,7 @@
           <t xml:space="preserve">parduota</t>
         </is>
       </c>
-      <c r="D11" s="2">
+      <c r="D11" s="2" t="n">
         <v>34942</v>
       </c>
       <c r="E11" s="0" t="inlineStr">
@@ -1845,7 +1855,7 @@
           <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
         </is>
       </c>
-      <c r="F11" s="2">
+      <c r="F11" s="2" t="n">
         <v>19578</v>
       </c>
       <c r="G11" s="0" t="inlineStr">
@@ -1868,16 +1878,16 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K11" s="2">
-        <v>1</v>
-      </c>
-      <c r="L11" s="2">
-        <v>0</v>
-      </c>
-      <c r="M11" s="3">
+      <c r="K11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="3" t="n">
         <v>2.88</v>
       </c>
-      <c r="N11" s="3">
+      <c r="N11" s="3" t="n">
         <v>2.01</v>
       </c>
     </row>
@@ -1897,7 +1907,7 @@
           <t xml:space="preserve">parduota</t>
         </is>
       </c>
-      <c r="D12" s="2">
+      <c r="D12" s="2" t="n">
         <v>34942</v>
       </c>
       <c r="E12" s="0" t="inlineStr">
@@ -1905,7 +1915,7 @@
           <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
         </is>
       </c>
-      <c r="F12" s="2">
+      <c r="F12" s="2" t="n">
         <v>19590</v>
       </c>
       <c r="G12" s="0" t="inlineStr">
@@ -1928,16 +1938,16 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K12" s="2">
-        <v>1</v>
-      </c>
-      <c r="L12" s="2">
-        <v>0</v>
-      </c>
-      <c r="M12" s="3">
+      <c r="K12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="3" t="n">
         <v>2.77</v>
       </c>
-      <c r="N12" s="3">
+      <c r="N12" s="3" t="n">
         <v>2.01</v>
       </c>
     </row>
@@ -1957,7 +1967,7 @@
           <t xml:space="preserve">parduota</t>
         </is>
       </c>
-      <c r="D13" s="2">
+      <c r="D13" s="2" t="n">
         <v>34942</v>
       </c>
       <c r="E13" s="0" t="inlineStr">
@@ -1965,7 +1975,7 @@
           <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
         </is>
       </c>
-      <c r="F13" s="2">
+      <c r="F13" s="2" t="n">
         <v>19582</v>
       </c>
       <c r="G13" s="0" t="inlineStr">
@@ -1988,16 +1998,16 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K13" s="2">
-        <v>1</v>
-      </c>
-      <c r="L13" s="2">
-        <v>0</v>
-      </c>
-      <c r="M13" s="3">
+      <c r="K13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3" t="n">
         <v>2.97</v>
       </c>
-      <c r="N13" s="3">
+      <c r="N13" s="3" t="n">
         <v>2.01</v>
       </c>
     </row>
@@ -2017,7 +2027,7 @@
           <t xml:space="preserve">parduota</t>
         </is>
       </c>
-      <c r="D14" s="2">
+      <c r="D14" s="2" t="n">
         <v>34942</v>
       </c>
       <c r="E14" s="0" t="inlineStr">
@@ -2025,7 +2035,7 @@
           <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
         </is>
       </c>
-      <c r="F14" s="2">
+      <c r="F14" s="2" t="n">
         <v>19562</v>
       </c>
       <c r="G14" s="0" t="inlineStr">
@@ -2048,16 +2058,16 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K14" s="2">
-        <v>1</v>
-      </c>
-      <c r="L14" s="2">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3">
+      <c r="K14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3" t="n">
         <v>2.88</v>
       </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="n">
         <v>2.01</v>
       </c>
     </row>
@@ -2077,7 +2087,7 @@
           <t xml:space="preserve">parduota</t>
         </is>
       </c>
-      <c r="D15" s="2">
+      <c r="D15" s="2" t="n">
         <v>34942</v>
       </c>
       <c r="E15" s="0" t="inlineStr">
@@ -2085,7 +2095,7 @@
           <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
         </is>
       </c>
-      <c r="F15" s="2">
+      <c r="F15" s="2" t="n">
         <v>19570</v>
       </c>
       <c r="G15" s="0" t="inlineStr">
@@ -2108,16 +2118,16 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K15" s="2">
+      <c r="K15" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="L15" s="2">
-        <v>0</v>
-      </c>
-      <c r="M15" s="3">
+      <c r="L15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="3" t="n">
         <v>19.61</v>
       </c>
-      <c r="N15" s="3">
+      <c r="N15" s="3" t="n">
         <v>14.07</v>
       </c>
     </row>
@@ -2164,16 +2174,16 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K16" s="2">
-        <v>1</v>
-      </c>
-      <c r="L16" s="2">
-        <v>0</v>
-      </c>
-      <c r="M16" s="3">
+      <c r="K16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="3" t="n">
         <v>62.22</v>
       </c>
-      <c r="N16" s="3">
+      <c r="N16" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2220,16 +2230,16 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K17" s="2">
-        <v>1</v>
-      </c>
-      <c r="L17" s="2">
-        <v>0</v>
-      </c>
-      <c r="M17" s="3">
+      <c r="K17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="3" t="n">
         <v>8.8</v>
       </c>
-      <c r="N17" s="3">
+      <c r="N17" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2276,16 +2286,16 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K18" s="2">
+      <c r="K18" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="L18" s="2">
-        <v>0</v>
-      </c>
-      <c r="M18" s="3">
+      <c r="L18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="3" t="n">
         <v>167.74</v>
       </c>
-      <c r="N18" s="3">
+      <c r="N18" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2305,7 +2315,7 @@
           <t xml:space="preserve">parduota_sd</t>
         </is>
       </c>
-      <c r="D19" s="2">
+      <c r="D19" s="2" t="n">
         <v>34942</v>
       </c>
       <c r="E19" s="0" t="inlineStr">
@@ -2334,16 +2344,16 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K19" s="2">
-        <v>1</v>
-      </c>
-      <c r="L19" s="2">
-        <v>0</v>
-      </c>
-      <c r="M19" s="3">
+      <c r="K19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="3" t="n">
         <v>48.12</v>
       </c>
-      <c r="N19" s="3">
+      <c r="N19" s="3" t="n">
         <v>0.66</v>
       </c>
     </row>
@@ -2363,7 +2373,7 @@
           <t xml:space="preserve">dovana</t>
         </is>
       </c>
-      <c r="D20" s="2">
+      <c r="D20" s="2" t="n">
         <v>34942</v>
       </c>
       <c r="E20" s="0" t="inlineStr">
@@ -2371,7 +2381,7 @@
           <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
         </is>
       </c>
-      <c r="F20" s="2">
+      <c r="F20" s="2" t="n">
         <v>16305</v>
       </c>
       <c r="G20" s="0" t="inlineStr">
@@ -2394,16 +2404,16 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K20" s="2">
-        <v>1</v>
-      </c>
-      <c r="L20" s="2">
-        <v>0</v>
-      </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
-      <c r="N20" s="3">
+      <c r="K20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3" t="n">
         <v>0.66</v>
       </c>
     </row>
@@ -2423,7 +2433,7 @@
           <t xml:space="preserve">atidare</t>
         </is>
       </c>
-      <c r="D21" s="2">
+      <c r="D21" s="2" t="n">
         <v>34942</v>
       </c>
       <c r="E21" s="0" t="inlineStr">
@@ -2452,16 +2462,16 @@
           <t xml:space="preserve">desktop</t>
         </is>
       </c>
-      <c r="K21" s="2">
+      <c r="K21" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="L21" s="2">
+      <c r="L21" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="M21" s="3">
-        <v>0</v>
-      </c>
-      <c r="N21" s="3">
+      <c r="M21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2481,7 +2491,7 @@
           <t xml:space="preserve">dovana_atrakinta</t>
         </is>
       </c>
-      <c r="D22" s="2">
+      <c r="D22" s="2" t="n">
         <v>34942</v>
       </c>
       <c r="E22" s="0" t="inlineStr">
@@ -2510,16 +2520,16 @@
           <t xml:space="preserve">desktop</t>
         </is>
       </c>
-      <c r="K22" s="2">
+      <c r="K22" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="L22" s="2">
+      <c r="L22" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
-      </c>
-      <c r="N22" s="3">
+      <c r="M22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2539,7 +2549,7 @@
           <t xml:space="preserve">dovana_rinko</t>
         </is>
       </c>
-      <c r="D23" s="2">
+      <c r="D23" s="2" t="n">
         <v>34942</v>
       </c>
       <c r="E23" s="0" t="inlineStr">
@@ -2568,16 +2578,16 @@
           <t xml:space="preserve">desktop</t>
         </is>
       </c>
-      <c r="K23" s="2">
-        <v>1</v>
-      </c>
-      <c r="L23" s="2">
-        <v>1</v>
-      </c>
-      <c r="M23" s="3">
-        <v>0</v>
-      </c>
-      <c r="N23" s="3">
+      <c r="K23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2597,7 +2607,7 @@
           <t xml:space="preserve">dovana_rinko</t>
         </is>
       </c>
-      <c r="D24" s="2">
+      <c r="D24" s="2" t="n">
         <v>34942</v>
       </c>
       <c r="E24" s="0" t="inlineStr">
@@ -2605,7 +2615,7 @@
           <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
         </is>
       </c>
-      <c r="F24" s="2">
+      <c r="F24" s="2" t="n">
         <v>17386</v>
       </c>
       <c r="G24" s="0" t="inlineStr">
@@ -2628,16 +2638,16 @@
           <t xml:space="preserve">desktop</t>
         </is>
       </c>
-      <c r="K24" s="2">
-        <v>1</v>
-      </c>
-      <c r="L24" s="2">
-        <v>1</v>
-      </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
-      <c r="N24" s="3">
+      <c r="K24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2657,7 +2667,7 @@
           <t xml:space="preserve">dydis_perjunge</t>
         </is>
       </c>
-      <c r="D25" s="2">
+      <c r="D25" s="2" t="n">
         <v>34942</v>
       </c>
       <c r="E25" s="0" t="inlineStr">
@@ -2686,16 +2696,16 @@
           <t xml:space="preserve">desktop</t>
         </is>
       </c>
-      <c r="K25" s="2">
-        <v>1</v>
-      </c>
-      <c r="L25" s="2">
-        <v>1</v>
-      </c>
-      <c r="M25" s="3">
-        <v>0</v>
-      </c>
-      <c r="N25" s="3">
+      <c r="K25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2715,7 +2725,7 @@
           <t xml:space="preserve">idejo</t>
         </is>
       </c>
-      <c r="D26" s="2">
+      <c r="D26" s="2" t="n">
         <v>34942</v>
       </c>
       <c r="E26" s="0" t="inlineStr">
@@ -2723,7 +2733,7 @@
           <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
         </is>
       </c>
-      <c r="F26" s="2">
+      <c r="F26" s="2" t="n">
         <v>19471</v>
       </c>
       <c r="G26" s="0" t="inlineStr">
@@ -2746,16 +2756,16 @@
           <t xml:space="preserve">desktop</t>
         </is>
       </c>
-      <c r="K26" s="2">
+      <c r="K26" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="L26" s="2">
+      <c r="L26" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M26" s="3">
-        <v>0</v>
-      </c>
-      <c r="N26" s="3">
+      <c r="M26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2775,7 +2785,7 @@
           <t xml:space="preserve">idejo</t>
         </is>
       </c>
-      <c r="D27" s="2">
+      <c r="D27" s="2" t="n">
         <v>34942</v>
       </c>
       <c r="E27" s="0" t="inlineStr">
@@ -2783,7 +2793,7 @@
           <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
         </is>
       </c>
-      <c r="F27" s="2">
+      <c r="F27" s="2" t="n">
         <v>19479</v>
       </c>
       <c r="G27" s="0" t="inlineStr">
@@ -2806,16 +2816,16 @@
           <t xml:space="preserve">desktop</t>
         </is>
       </c>
-      <c r="K27" s="2">
+      <c r="K27" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="L27" s="2">
+      <c r="L27" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M27" s="3">
-        <v>0</v>
-      </c>
-      <c r="N27" s="3">
+      <c r="M27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2835,7 +2845,7 @@
           <t xml:space="preserve">idejo</t>
         </is>
       </c>
-      <c r="D28" s="2">
+      <c r="D28" s="2" t="n">
         <v>34942</v>
       </c>
       <c r="E28" s="0" t="inlineStr">
@@ -2843,7 +2853,7 @@
           <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
         </is>
       </c>
-      <c r="F28" s="2">
+      <c r="F28" s="2" t="n">
         <v>19488</v>
       </c>
       <c r="G28" s="0" t="inlineStr">
@@ -2866,16 +2876,16 @@
           <t xml:space="preserve">desktop</t>
         </is>
       </c>
-      <c r="K28" s="2">
+      <c r="K28" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="L28" s="2">
+      <c r="L28" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M28" s="3">
-        <v>0</v>
-      </c>
-      <c r="N28" s="3">
+      <c r="M28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2895,7 +2905,7 @@
           <t xml:space="preserve">idejo</t>
         </is>
       </c>
-      <c r="D29" s="2">
+      <c r="D29" s="2" t="n">
         <v>34942</v>
       </c>
       <c r="E29" s="0" t="inlineStr">
@@ -2903,7 +2913,7 @@
           <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
         </is>
       </c>
-      <c r="F29" s="2">
+      <c r="F29" s="2" t="n">
         <v>19496</v>
       </c>
       <c r="G29" s="0" t="inlineStr">
@@ -2926,16 +2936,16 @@
           <t xml:space="preserve">desktop</t>
         </is>
       </c>
-      <c r="K29" s="2">
+      <c r="K29" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="L29" s="2">
+      <c r="L29" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M29" s="3">
-        <v>0</v>
-      </c>
-      <c r="N29" s="3">
+      <c r="M29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2955,7 +2965,7 @@
           <t xml:space="preserve">idejo</t>
         </is>
       </c>
-      <c r="D30" s="2">
+      <c r="D30" s="2" t="n">
         <v>34942</v>
       </c>
       <c r="E30" s="0" t="inlineStr">
@@ -2963,7 +2973,7 @@
           <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
         </is>
       </c>
-      <c r="F30" s="2">
+      <c r="F30" s="2" t="n">
         <v>19504</v>
       </c>
       <c r="G30" s="0" t="inlineStr">
@@ -2986,16 +2996,16 @@
           <t xml:space="preserve">desktop</t>
         </is>
       </c>
-      <c r="K30" s="2">
+      <c r="K30" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="L30" s="2">
+      <c r="L30" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M30" s="3">
-        <v>0</v>
-      </c>
-      <c r="N30" s="3">
+      <c r="M30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3015,7 +3025,7 @@
           <t xml:space="preserve">idejo</t>
         </is>
       </c>
-      <c r="D31" s="2">
+      <c r="D31" s="2" t="n">
         <v>34942</v>
       </c>
       <c r="E31" s="0" t="inlineStr">
@@ -3023,7 +3033,7 @@
           <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
         </is>
       </c>
-      <c r="F31" s="2">
+      <c r="F31" s="2" t="n">
         <v>19538</v>
       </c>
       <c r="G31" s="0" t="inlineStr">
@@ -3046,16 +3056,16 @@
           <t xml:space="preserve">desktop</t>
         </is>
       </c>
-      <c r="K31" s="2">
+      <c r="K31" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="L31" s="2">
+      <c r="L31" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M31" s="3">
-        <v>0</v>
-      </c>
-      <c r="N31" s="3">
+      <c r="M31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3075,7 +3085,7 @@
           <t xml:space="preserve">idejo</t>
         </is>
       </c>
-      <c r="D32" s="2">
+      <c r="D32" s="2" t="n">
         <v>34942</v>
       </c>
       <c r="E32" s="0" t="inlineStr">
@@ -3083,7 +3093,7 @@
           <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
         </is>
       </c>
-      <c r="F32" s="2">
+      <c r="F32" s="2" t="n">
         <v>19562</v>
       </c>
       <c r="G32" s="0" t="inlineStr">
@@ -3106,16 +3116,16 @@
           <t xml:space="preserve">desktop</t>
         </is>
       </c>
-      <c r="K32" s="2">
+      <c r="K32" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="L32" s="2">
+      <c r="L32" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
-      <c r="N32" s="3">
+      <c r="M32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3135,7 +3145,7 @@
           <t xml:space="preserve">idejo</t>
         </is>
       </c>
-      <c r="D33" s="2">
+      <c r="D33" s="2" t="n">
         <v>34942</v>
       </c>
       <c r="E33" s="0" t="inlineStr">
@@ -3143,7 +3153,7 @@
           <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
         </is>
       </c>
-      <c r="F33" s="2">
+      <c r="F33" s="2" t="n">
         <v>19570</v>
       </c>
       <c r="G33" s="0" t="inlineStr">
@@ -3166,16 +3176,16 @@
           <t xml:space="preserve">desktop</t>
         </is>
       </c>
-      <c r="K33" s="2">
+      <c r="K33" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="L33" s="2">
+      <c r="L33" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M33" s="3">
-        <v>0</v>
-      </c>
-      <c r="N33" s="3">
+      <c r="M33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3195,7 +3205,7 @@
           <t xml:space="preserve">idejo</t>
         </is>
       </c>
-      <c r="D34" s="2">
+      <c r="D34" s="2" t="n">
         <v>34942</v>
       </c>
       <c r="E34" s="0" t="inlineStr">
@@ -3203,7 +3213,7 @@
           <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
         </is>
       </c>
-      <c r="F34" s="2">
+      <c r="F34" s="2" t="n">
         <v>19578</v>
       </c>
       <c r="G34" s="0" t="inlineStr">
@@ -3226,16 +3236,16 @@
           <t xml:space="preserve">desktop</t>
         </is>
       </c>
-      <c r="K34" s="2">
+      <c r="K34" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="L34" s="2">
+      <c r="L34" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M34" s="3">
-        <v>0</v>
-      </c>
-      <c r="N34" s="3">
+      <c r="M34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3255,7 +3265,7 @@
           <t xml:space="preserve">idejo</t>
         </is>
       </c>
-      <c r="D35" s="2">
+      <c r="D35" s="2" t="n">
         <v>34942</v>
       </c>
       <c r="E35" s="0" t="inlineStr">
@@ -3263,7 +3273,7 @@
           <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
         </is>
       </c>
-      <c r="F35" s="2">
+      <c r="F35" s="2" t="n">
         <v>19582</v>
       </c>
       <c r="G35" s="0" t="inlineStr">
@@ -3286,16 +3296,16 @@
           <t xml:space="preserve">desktop</t>
         </is>
       </c>
-      <c r="K35" s="2">
+      <c r="K35" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="L35" s="2">
+      <c r="L35" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M35" s="3">
-        <v>0</v>
-      </c>
-      <c r="N35" s="3">
+      <c r="M35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3315,7 +3325,7 @@
           <t xml:space="preserve">idejo</t>
         </is>
       </c>
-      <c r="D36" s="2">
+      <c r="D36" s="2" t="n">
         <v>34942</v>
       </c>
       <c r="E36" s="0" t="inlineStr">
@@ -3323,7 +3333,7 @@
           <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
         </is>
       </c>
-      <c r="F36" s="2">
+      <c r="F36" s="2" t="n">
         <v>19590</v>
       </c>
       <c r="G36" s="0" t="inlineStr">
@@ -3346,16 +3356,16 @@
           <t xml:space="preserve">desktop</t>
         </is>
       </c>
-      <c r="K36" s="2">
+      <c r="K36" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="L36" s="2">
+      <c r="L36" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M36" s="3">
-        <v>0</v>
-      </c>
-      <c r="N36" s="3">
+      <c r="M36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3375,7 +3385,7 @@
           <t xml:space="preserve">iseme</t>
         </is>
       </c>
-      <c r="D37" s="2">
+      <c r="D37" s="2" t="n">
         <v>34942</v>
       </c>
       <c r="E37" s="0" t="inlineStr">
@@ -3383,7 +3393,7 @@
           <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
         </is>
       </c>
-      <c r="F37" s="2">
+      <c r="F37" s="2" t="n">
         <v>19570</v>
       </c>
       <c r="G37" s="0" t="inlineStr">
@@ -3406,16 +3416,16 @@
           <t xml:space="preserve">desktop</t>
         </is>
       </c>
-      <c r="K37" s="2">
-        <v>1</v>
-      </c>
-      <c r="L37" s="2">
-        <v>1</v>
-      </c>
-      <c r="M37" s="3">
-        <v>0</v>
-      </c>
-      <c r="N37" s="3">
+      <c r="K37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3435,7 +3445,7 @@
           <t xml:space="preserve">krepselis</t>
         </is>
       </c>
-      <c r="D38" s="2">
+      <c r="D38" s="2" t="n">
         <v>34942</v>
       </c>
       <c r="E38" s="0" t="inlineStr">
@@ -3464,16 +3474,16 @@
           <t xml:space="preserve">desktop</t>
         </is>
       </c>
-      <c r="K38" s="2">
-        <v>1</v>
-      </c>
-      <c r="L38" s="2">
-        <v>1</v>
-      </c>
-      <c r="M38" s="3">
-        <v>0</v>
-      </c>
-      <c r="N38" s="3">
+      <c r="K38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3493,7 +3503,7 @@
           <t xml:space="preserve">min_pasiekta</t>
         </is>
       </c>
-      <c r="D39" s="2">
+      <c r="D39" s="2" t="n">
         <v>34942</v>
       </c>
       <c r="E39" s="0" t="inlineStr">
@@ -3522,16 +3532,16 @@
           <t xml:space="preserve">desktop</t>
         </is>
       </c>
-      <c r="K39" s="2">
+      <c r="K39" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="L39" s="2">
+      <c r="L39" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M39" s="3">
-        <v>0</v>
-      </c>
-      <c r="N39" s="3">
+      <c r="M39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3551,7 +3561,7 @@
           <t xml:space="preserve">rodyta</t>
         </is>
       </c>
-      <c r="D40" s="2">
+      <c r="D40" s="2" t="n">
         <v>34942</v>
       </c>
       <c r="E40" s="0" t="inlineStr">
@@ -3559,7 +3569,7 @@
           <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
         </is>
       </c>
-      <c r="F40" s="2">
+      <c r="F40" s="2" t="n">
         <v>19471</v>
       </c>
       <c r="G40" s="0" t="inlineStr">
@@ -3582,16 +3592,16 @@
           <t xml:space="preserve">desktop</t>
         </is>
       </c>
-      <c r="K40" s="2">
+      <c r="K40" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="L40" s="2">
+      <c r="L40" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M40" s="3">
-        <v>0</v>
-      </c>
-      <c r="N40" s="3">
+      <c r="M40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3611,7 +3621,7 @@
           <t xml:space="preserve">rodyta</t>
         </is>
       </c>
-      <c r="D41" s="2">
+      <c r="D41" s="2" t="n">
         <v>34942</v>
       </c>
       <c r="E41" s="0" t="inlineStr">
@@ -3619,7 +3629,7 @@
           <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
         </is>
       </c>
-      <c r="F41" s="2">
+      <c r="F41" s="2" t="n">
         <v>19479</v>
       </c>
       <c r="G41" s="0" t="inlineStr">
@@ -3642,16 +3652,16 @@
           <t xml:space="preserve">desktop</t>
         </is>
       </c>
-      <c r="K41" s="2">
+      <c r="K41" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="L41" s="2">
+      <c r="L41" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M41" s="3">
-        <v>0</v>
-      </c>
-      <c r="N41" s="3">
+      <c r="M41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3671,7 +3681,7 @@
           <t xml:space="preserve">rodyta</t>
         </is>
       </c>
-      <c r="D42" s="2">
+      <c r="D42" s="2" t="n">
         <v>34942</v>
       </c>
       <c r="E42" s="0" t="inlineStr">
@@ -3679,7 +3689,7 @@
           <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
         </is>
       </c>
-      <c r="F42" s="2">
+      <c r="F42" s="2" t="n">
         <v>19488</v>
       </c>
       <c r="G42" s="0" t="inlineStr">
@@ -3702,16 +3712,16 @@
           <t xml:space="preserve">desktop</t>
         </is>
       </c>
-      <c r="K42" s="2">
+      <c r="K42" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="L42" s="2">
+      <c r="L42" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
-      <c r="N42" s="3">
+      <c r="M42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3731,7 +3741,7 @@
           <t xml:space="preserve">rodyta</t>
         </is>
       </c>
-      <c r="D43" s="2">
+      <c r="D43" s="2" t="n">
         <v>34942</v>
       </c>
       <c r="E43" s="0" t="inlineStr">
@@ -3739,7 +3749,7 @@
           <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
         </is>
       </c>
-      <c r="F43" s="2">
+      <c r="F43" s="2" t="n">
         <v>19496</v>
       </c>
       <c r="G43" s="0" t="inlineStr">
@@ -3762,16 +3772,16 @@
           <t xml:space="preserve">desktop</t>
         </is>
       </c>
-      <c r="K43" s="2">
+      <c r="K43" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="L43" s="2">
+      <c r="L43" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
-      </c>
-      <c r="N43" s="3">
+      <c r="M43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3791,7 +3801,7 @@
           <t xml:space="preserve">rodyta</t>
         </is>
       </c>
-      <c r="D44" s="2">
+      <c r="D44" s="2" t="n">
         <v>34942</v>
       </c>
       <c r="E44" s="0" t="inlineStr">
@@ -3799,7 +3809,7 @@
           <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
         </is>
       </c>
-      <c r="F44" s="2">
+      <c r="F44" s="2" t="n">
         <v>19504</v>
       </c>
       <c r="G44" s="0" t="inlineStr">
@@ -3822,16 +3832,16 @@
           <t xml:space="preserve">desktop</t>
         </is>
       </c>
-      <c r="K44" s="2">
+      <c r="K44" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="L44" s="2">
+      <c r="L44" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
-      </c>
-      <c r="N44" s="3">
+      <c r="M44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3851,7 +3861,7 @@
           <t xml:space="preserve">rodyta</t>
         </is>
       </c>
-      <c r="D45" s="2">
+      <c r="D45" s="2" t="n">
         <v>34942</v>
       </c>
       <c r="E45" s="0" t="inlineStr">
@@ -3859,7 +3869,7 @@
           <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
         </is>
       </c>
-      <c r="F45" s="2">
+      <c r="F45" s="2" t="n">
         <v>19538</v>
       </c>
       <c r="G45" s="0" t="inlineStr">
@@ -3882,16 +3892,16 @@
           <t xml:space="preserve">desktop</t>
         </is>
       </c>
-      <c r="K45" s="2">
+      <c r="K45" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="L45" s="2">
+      <c r="L45" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M45" s="3">
-        <v>0</v>
-      </c>
-      <c r="N45" s="3">
+      <c r="M45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3911,7 +3921,7 @@
           <t xml:space="preserve">rodyta</t>
         </is>
       </c>
-      <c r="D46" s="2">
+      <c r="D46" s="2" t="n">
         <v>34942</v>
       </c>
       <c r="E46" s="0" t="inlineStr">
@@ -3919,7 +3929,7 @@
           <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
         </is>
       </c>
-      <c r="F46" s="2">
+      <c r="F46" s="2" t="n">
         <v>19562</v>
       </c>
       <c r="G46" s="0" t="inlineStr">
@@ -3942,16 +3952,16 @@
           <t xml:space="preserve">desktop</t>
         </is>
       </c>
-      <c r="K46" s="2">
+      <c r="K46" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="L46" s="2">
+      <c r="L46" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M46" s="3">
-        <v>0</v>
-      </c>
-      <c r="N46" s="3">
+      <c r="M46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3971,7 +3981,7 @@
           <t xml:space="preserve">rodyta</t>
         </is>
       </c>
-      <c r="D47" s="2">
+      <c r="D47" s="2" t="n">
         <v>34942</v>
       </c>
       <c r="E47" s="0" t="inlineStr">
@@ -3979,7 +3989,7 @@
           <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
         </is>
       </c>
-      <c r="F47" s="2">
+      <c r="F47" s="2" t="n">
         <v>19570</v>
       </c>
       <c r="G47" s="0" t="inlineStr">
@@ -4002,16 +4012,16 @@
           <t xml:space="preserve">desktop</t>
         </is>
       </c>
-      <c r="K47" s="2">
+      <c r="K47" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="L47" s="2">
+      <c r="L47" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
-      </c>
-      <c r="N47" s="3">
+      <c r="M47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4031,7 +4041,7 @@
           <t xml:space="preserve">rodyta</t>
         </is>
       </c>
-      <c r="D48" s="2">
+      <c r="D48" s="2" t="n">
         <v>34942</v>
       </c>
       <c r="E48" s="0" t="inlineStr">
@@ -4039,7 +4049,7 @@
           <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
         </is>
       </c>
-      <c r="F48" s="2">
+      <c r="F48" s="2" t="n">
         <v>19578</v>
       </c>
       <c r="G48" s="0" t="inlineStr">
@@ -4062,16 +4072,16 @@
           <t xml:space="preserve">desktop</t>
         </is>
       </c>
-      <c r="K48" s="2">
+      <c r="K48" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="L48" s="2">
+      <c r="L48" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M48" s="3">
-        <v>0</v>
-      </c>
-      <c r="N48" s="3">
+      <c r="M48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4091,7 +4101,7 @@
           <t xml:space="preserve">rodyta</t>
         </is>
       </c>
-      <c r="D49" s="2">
+      <c r="D49" s="2" t="n">
         <v>34942</v>
       </c>
       <c r="E49" s="0" t="inlineStr">
@@ -4099,7 +4109,7 @@
           <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
         </is>
       </c>
-      <c r="F49" s="2">
+      <c r="F49" s="2" t="n">
         <v>19582</v>
       </c>
       <c r="G49" s="0" t="inlineStr">
@@ -4122,16 +4132,16 @@
           <t xml:space="preserve">desktop</t>
         </is>
       </c>
-      <c r="K49" s="2">
+      <c r="K49" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="L49" s="2">
+      <c r="L49" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M49" s="3">
-        <v>0</v>
-      </c>
-      <c r="N49" s="3">
+      <c r="M49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4151,7 +4161,7 @@
           <t xml:space="preserve">rodyta</t>
         </is>
       </c>
-      <c r="D50" s="2">
+      <c r="D50" s="2" t="n">
         <v>34942</v>
       </c>
       <c r="E50" s="0" t="inlineStr">
@@ -4159,7 +4169,7 @@
           <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
         </is>
       </c>
-      <c r="F50" s="2">
+      <c r="F50" s="2" t="n">
         <v>19590</v>
       </c>
       <c r="G50" s="0" t="inlineStr">
@@ -4182,16 +4192,16 @@
           <t xml:space="preserve">desktop</t>
         </is>
       </c>
-      <c r="K50" s="2">
+      <c r="K50" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="L50" s="2">
+      <c r="L50" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M50" s="3">
-        <v>0</v>
-      </c>
-      <c r="N50" s="3">
+      <c r="M50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4211,7 +4221,7 @@
           <t xml:space="preserve">iseme_p1</t>
         </is>
       </c>
-      <c r="D51" s="2">
+      <c r="D51" s="2" t="n">
         <v>34942</v>
       </c>
       <c r="E51" s="0" t="inlineStr">
@@ -4219,7 +4229,7 @@
           <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
         </is>
       </c>
-      <c r="F51" s="2">
+      <c r="F51" s="2" t="n">
         <v>19570</v>
       </c>
       <c r="G51" s="0" t="inlineStr">
@@ -4242,16 +4252,16 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K51" s="2">
-        <v>1</v>
-      </c>
-      <c r="L51" s="2">
-        <v>0</v>
-      </c>
-      <c r="M51" s="3">
-        <v>0</v>
-      </c>
-      <c r="N51" s="3">
+      <c r="K51" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4271,7 +4281,7 @@
           <t xml:space="preserve">atidare</t>
         </is>
       </c>
-      <c r="D52" s="2">
+      <c r="D52" s="2" t="n">
         <v>34942</v>
       </c>
       <c r="E52" s="0" t="inlineStr">
@@ -4300,16 +4310,16 @@
           <t xml:space="preserve">desktop</t>
         </is>
       </c>
-      <c r="K52" s="2">
-        <v>0</v>
-      </c>
-      <c r="L52" s="2">
+      <c r="K52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="M52" s="3">
-        <v>0</v>
-      </c>
-      <c r="N52" s="3">
+      <c r="M52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4329,7 +4339,7 @@
           <t xml:space="preserve">idejo</t>
         </is>
       </c>
-      <c r="D53" s="2">
+      <c r="D53" s="2" t="n">
         <v>34942</v>
       </c>
       <c r="E53" s="0" t="inlineStr">
@@ -4358,16 +4368,16 @@
           <t xml:space="preserve">desktop</t>
         </is>
       </c>
-      <c r="K53" s="2">
-        <v>0</v>
-      </c>
-      <c r="L53" s="2">
+      <c r="K53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M53" s="3">
-        <v>0</v>
-      </c>
-      <c r="N53" s="3">
+      <c r="M53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4387,7 +4397,7 @@
           <t xml:space="preserve">krepselis</t>
         </is>
       </c>
-      <c r="D54" s="2">
+      <c r="D54" s="2" t="n">
         <v>34942</v>
       </c>
       <c r="E54" s="0" t="inlineStr">
@@ -4416,16 +4426,16 @@
           <t xml:space="preserve">desktop</t>
         </is>
       </c>
-      <c r="K54" s="2">
-        <v>0</v>
-      </c>
-      <c r="L54" s="2">
-        <v>1</v>
-      </c>
-      <c r="M54" s="3">
-        <v>0</v>
-      </c>
-      <c r="N54" s="3">
+      <c r="K54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4445,7 +4455,7 @@
           <t xml:space="preserve">min_pasiekta</t>
         </is>
       </c>
-      <c r="D55" s="2">
+      <c r="D55" s="2" t="n">
         <v>34942</v>
       </c>
       <c r="E55" s="0" t="inlineStr">
@@ -4474,16 +4484,16 @@
           <t xml:space="preserve">desktop</t>
         </is>
       </c>
-      <c r="K55" s="2">
-        <v>0</v>
-      </c>
-      <c r="L55" s="2">
+      <c r="K55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M55" s="3">
-        <v>0</v>
-      </c>
-      <c r="N55" s="3">
+      <c r="M55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4503,7 +4513,7 @@
           <t xml:space="preserve">kabliukas</t>
         </is>
       </c>
-      <c r="D56" s="2">
+      <c r="D56" s="2" t="n">
         <v>34942</v>
       </c>
       <c r="E56" s="0" t="inlineStr">
@@ -4511,7 +4521,7 @@
           <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
         </is>
       </c>
-      <c r="F56" s="2">
+      <c r="F56" s="2" t="n">
         <v>19570</v>
       </c>
       <c r="G56" s="0" t="inlineStr">
@@ -4534,16 +4544,16 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K56" s="2">
+      <c r="K56" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="L56" s="2">
+      <c r="L56" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M56" s="3">
-        <v>0</v>
-      </c>
-      <c r="N56" s="3">
+      <c r="M56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4563,7 +4573,7 @@
           <t xml:space="preserve">riba_pasieke</t>
         </is>
       </c>
-      <c r="D57" s="2">
+      <c r="D57" s="2" t="n">
         <v>34942</v>
       </c>
       <c r="E57" s="0" t="inlineStr">
@@ -4592,16 +4602,16 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K57" s="2">
+      <c r="K57" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="L57" s="2">
+      <c r="L57" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M57" s="3">
-        <v>0</v>
-      </c>
-      <c r="N57" s="3">
+      <c r="M57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4621,7 +4631,7 @@
           <t xml:space="preserve">uzdarytoja</t>
         </is>
       </c>
-      <c r="D58" s="2">
+      <c r="D58" s="2" t="n">
         <v>34942</v>
       </c>
       <c r="E58" s="0" t="inlineStr">
@@ -4629,7 +4639,7 @@
           <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
         </is>
       </c>
-      <c r="F58" s="2">
+      <c r="F58" s="2" t="n">
         <v>19570</v>
       </c>
       <c r="G58" s="0" t="inlineStr">
@@ -4652,16 +4662,16 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K58" s="2">
-        <v>1</v>
-      </c>
-      <c r="L58" s="2">
-        <v>1</v>
-      </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
-      <c r="N58" s="3">
+      <c r="K58" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L58" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4681,7 +4691,7 @@
           <t xml:space="preserve">riba_pasieke_krepselis</t>
         </is>
       </c>
-      <c r="D59" s="2">
+      <c r="D59" s="2" t="n">
         <v>34942</v>
       </c>
       <c r="E59" s="0" t="inlineStr">
@@ -4710,20 +4720,20 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K59" s="2">
-        <v>1</v>
-      </c>
-      <c r="L59" s="2">
-        <v>1</v>
-      </c>
-      <c r="M59" s="3">
-        <v>0</v>
-      </c>
-      <c r="N59" s="3">
+      <c r="K59" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L59" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" s="3" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <sheetViews/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/screenshots/testas.xlsx
+++ b/screenshots/testas.xlsx
@@ -3,10 +3,11 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
     <sheet name="Kaip skaityti" sheetId="1" r:id="rId1"/>
-    <sheet name="Rinkiniai" sheetId="2" r:id="rId2"/>
-    <sheet name="Kanibalizacija" sheetId="3" r:id="rId3"/>
-    <sheet name="DP pakopos" sheetId="4" r:id="rId4"/>
-    <sheet name="Žali duomenys" sheetId="5" r:id="rId5"/>
+    <sheet name="Suvestinė" sheetId="2" r:id="rId2"/>
+    <sheet name="Prekės" sheetId="3" r:id="rId3"/>
+    <sheet name="Rinkiniai" sheetId="4" r:id="rId4"/>
+    <sheet name="Piltuvėlis" sheetId="5" r:id="rId5"/>
+    <sheet name="Žali duomenys" sheetId="6" r:id="rId6"/>
   </sheets>
 </workbook>
 </file>
@@ -71,7 +72,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B37"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -389,34 +390,6 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Šis failas — TIK paruošti rinkiniai ir DP pakai</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Surenkamos dėžės (kur klientas pats renka turinį) čia NERODOMOS —</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jos yra lange „Surenkami rinkiniai" ir jo Excel faile.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -424,23 +397,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9" customWidth="1"/>
-    <col min="2" max="2" width="44" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="11" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="12" customWidth="1"/>
-    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="1" max="1" width="26" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">PETSHOP — RINKINIAI (paruošti ir DP pakai)</t>
+          <t xml:space="preserve">PETSHOP — SURENKAMI RINKINIAI</t>
         </is>
       </c>
     </row>
@@ -464,7 +431,7 @@
       </c>
       <c r="B3" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-16 12:51</t>
+          <t xml:space="preserve">2026-08-16 12:55</t>
         </is>
       </c>
     </row>
@@ -478,77 +445,126 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ID</t>
+          <t xml:space="preserve">Rodiklis</t>
         </is>
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rinkinys</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tipas</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Parduota</t>
-        </is>
-      </c>
-      <c r="E5" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pajamos</t>
-        </is>
-      </c>
-      <c r="F5" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Savikaina</t>
-        </is>
-      </c>
-      <c r="G5" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pelnas</t>
-        </is>
-      </c>
-      <c r="H5" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Marža</t>
+          <t xml:space="preserve">Reikšmė</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Šiuo laikotarpiu paruoštų rinkinių ar DP pakų pardavimų nebuvo.</t>
-        </is>
+          <t xml:space="preserve">Pajamos su PVM</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>48.12</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
-        </is>
+          <t xml:space="preserve">Pelnas</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>4.49</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">SVARBU: tai NEREIŠKIA, kad pardavimų apskritai nebuvo.</t>
-        </is>
+          <t xml:space="preserve">Marža</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>0.12033</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Šis langas rodo tik PARUOŠTUS rinkinius (sudėtis nustatyta iš anksto) ir DP pakus.</t>
-        </is>
+          <t xml:space="preserve">Užsakymai su dėže</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">SURENKAMOS dėžės — kur klientas pats renkasi turinį — rodomos lange „Surenkami rinkiniai".</t>
+          <t xml:space="preserve">Vid. čekis</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>48.12</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vid. dydis (vnt.)</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Parduota vnt. viso</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Grąžinta</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dovanų savikaina</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eilutės be savikainos</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASTABA: eilutės be savikainos į maržą neįskaičiuotos — tikras pelnas mažesnis.</t>
         </is>
       </c>
     </row>
@@ -559,25 +575,29 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9" customWidth="1"/>
-    <col min="2" max="2" width="40" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="20" customWidth="1"/>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="46" customWidth="1"/>
+    <col min="3" max="3" width="13" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
     <col min="5" max="5" width="13" customWidth="1"/>
-    <col min="6" max="6" width="19" customWidth="1"/>
-    <col min="7" max="7" width="13" customWidth="1"/>
-    <col min="8" max="8" width="13" customWidth="1"/>
-    <col min="9" max="9" width="15" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="7" max="7" width="9" customWidth="1"/>
+    <col min="8" max="8" width="15" customWidth="1"/>
+    <col min="9" max="9" width="12" customWidth="1"/>
     <col min="10" max="10" width="12" customWidth="1"/>
+    <col min="11" max="11" width="12" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
+    <col min="13" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">KANIBALIZACIJA — ar rinkinys prideda, ar tik perkelia</t>
+          <t xml:space="preserve">PREKĖS DĖŽĖSE</t>
         </is>
       </c>
     </row>
@@ -601,7 +621,7 @@
       </c>
       <c r="B3" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-16 12:51</t>
+          <t xml:space="preserve">2026-08-16 12:55</t>
         </is>
       </c>
     </row>
@@ -613,81 +633,581 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Lyginama su</t>
-        </is>
-      </c>
-      <c r="B5" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-18 – 2026-07-17</t>
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prekės ID</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prekė</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Matė (sesijos)</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Įsidėjo (sesijos)</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Įdėjimo dalis</t>
+        </is>
+      </c>
+      <c r="F5" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Įdėta vnt.</t>
+        </is>
+      </c>
+      <c r="G5" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Išimta</t>
+        </is>
+      </c>
+      <c r="H5" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Išėmimo rodiklis</t>
+        </is>
+      </c>
+      <c r="I5" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Parduota vnt.</t>
+        </is>
+      </c>
+      <c r="J5" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pajamos</t>
+        </is>
+      </c>
+      <c r="K5" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Savikaina</t>
+        </is>
+      </c>
+      <c r="L5" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pelnas</t>
+        </is>
+      </c>
+      <c r="M5" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Marža</t>
+        </is>
+      </c>
+      <c r="N5" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dalis apyvartoje</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+      <c r="A6" s="2" t="n">
+        <v>19570</v>
+      </c>
+      <c r="B6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Animonda GranCarno Adult Beef: konservai šunims su šviežia jautiena, 800 g</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>0.111111</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>19.61</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>14.07</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="M6" s="4" t="n">
+        <v>0.132045</v>
+      </c>
+      <c r="N6" s="4" t="n">
+        <v>0.407523</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ID</t>
-        </is>
-      </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Rinkinys</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Vnt. rinkinyje</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Vnt. rinkinyje (buvo)</t>
-        </is>
-      </c>
-      <c r="E7" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Vnt. atskirai</t>
-        </is>
-      </c>
-      <c r="F7" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Vnt. atskirai (buvo)</t>
-        </is>
-      </c>
-      <c r="G7" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Iš viso dabar</t>
-        </is>
-      </c>
-      <c r="H7" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Iš viso buvo</t>
-        </is>
-      </c>
-      <c r="I7" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bendras pokytis</t>
-        </is>
-      </c>
-      <c r="J7" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Verdiktas</t>
-        </is>
+      <c r="A7" s="2" t="n">
+        <v>19582</v>
+      </c>
+      <c r="B7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Animonda GranCarno Adult Beef + Lamb: konserv</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="M7" s="4" t="n">
+        <v>0.179259</v>
+      </c>
+      <c r="N7" s="4" t="n">
+        <v>0.061721</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Šiuo laikotarpiu komponentų pardavimų nebuvo — palyginti nėra ko.</t>
-        </is>
+      <c r="A8" s="2" t="n">
+        <v>19538</v>
+      </c>
+      <c r="B8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Animonda GranCarno Adult Rumen: konservai suaugusiems šunims su galvijų prieskrandžiais, 800 g</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="M8" s="4" t="n">
+        <v>0.998148</v>
+      </c>
+      <c r="N8" s="4" t="n">
+        <v>0.061721</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>19578</v>
+      </c>
+      <c r="B9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Animonda GranCarno Adult Beef + Rabbit with Herbs: konservai suaugusiems šunims su šviežia jautiena ir triušiena, paskaninta žolelėmis, 800 g</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>0.666667</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" s="3" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="L9" s="3" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="M9" s="4" t="n">
+        <v>0.155451</v>
+      </c>
+      <c r="N9" s="4" t="n">
+        <v>0.05985</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>19562</v>
+      </c>
+      <c r="B10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Animonda GranCarno Adult Duck: konservai suaugusiems šunims su šviežia antiena, 800 g</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="3" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="L10" s="3" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="M10" s="4" t="n">
+        <v>0.155451</v>
+      </c>
+      <c r="N10" s="4" t="n">
+        <v>0.05985</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>19479</v>
+      </c>
+      <c r="B11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Animonda GranCarno Adult: konservai šunims su lašiša, praturtinta špinatais, 800 g</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" s="3" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="L11" s="3" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="M11" s="4" t="n">
+        <v>0.148596</v>
+      </c>
+      <c r="N11" s="4" t="n">
+        <v>0.059227</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>19496</v>
+      </c>
+      <c r="B12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Animonda GranCarno Adult: konservai suaugusiems šunims su žvėriena, 800 g</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>0.666667</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" s="3" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="L12" s="3" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="M12" s="4" t="n">
+        <v>0.148596</v>
+      </c>
+      <c r="N12" s="4" t="n">
+        <v>0.059227</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>19504</v>
+      </c>
+      <c r="B13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Animonda GranCarno Adult: konservai suaugusiems šunims su kalakutiena, 800 g</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>0.666667</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K13" s="3" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="L13" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M13" s="4" t="n">
+        <v>0.129643</v>
+      </c>
+      <c r="N13" s="4" t="n">
+        <v>0.058188</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>19471</v>
+      </c>
+      <c r="B14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Animonda GranCarno Adult: konservai šunims su širdimis, 800 g</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="M14" s="4" t="n">
+        <v>0.12231</v>
+      </c>
+      <c r="N14" s="4" t="n">
+        <v>0.057564</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>19488</v>
+      </c>
+      <c r="B15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Animonda GranCarno Adult: konservai šunims su elniena, pagardinta obuoliais, 800 g</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>0.666667</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" s="3" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="K15" s="3" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="L15" s="3" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="M15" s="4" t="n">
+        <v>0.12231</v>
+      </c>
+      <c r="N15" s="4" t="n">
+        <v>0.057564</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>19590</v>
+      </c>
+      <c r="B16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Animonda GranCarno Adult Beef + Duck Hearts: konservai suaugusiems šunims su jautiena ir ančių širdelėmis, 800 g</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" s="3" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="K16" s="3" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="L16" s="3" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="M16" s="4" t="n">
+        <v>0.12231</v>
+      </c>
+      <c r="N16" s="4" t="n">
+        <v>0.057564</v>
       </c>
     </row>
   </sheetData>
@@ -697,21 +1217,26 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9" customWidth="1"/>
-    <col min="2" max="2" width="40" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="11" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="10" customWidth="1"/>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="3" max="3" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="11" customWidth="1"/>
+    <col min="9" max="9" width="12" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
+    <col min="11" max="11" width="10" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">DP PAKOPOS</t>
+          <t xml:space="preserve">RINKINIAI IR DYDŽIAI</t>
         </is>
       </c>
     </row>
@@ -735,7 +1260,7 @@
       </c>
       <c r="B3" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-16 12:51</t>
+          <t xml:space="preserve">2026-08-16 12:55</t>
         </is>
       </c>
     </row>
@@ -749,33 +1274,97 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ID</t>
+          <t xml:space="preserve">Dėžės ID</t>
         </is>
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pakas</t>
+          <t xml:space="preserve">Rinkinys</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pakopa</t>
+          <t xml:space="preserve">Dydis</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Atidarė</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nupirko</t>
+        </is>
+      </c>
+      <c r="F5" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Konversija</t>
+        </is>
+      </c>
+      <c r="G5" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Parduota</t>
         </is>
       </c>
-      <c r="E5" s="1" t="inlineStr">
+      <c r="H5" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vid. dydis</t>
+        </is>
+      </c>
+      <c r="I5" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Pajamos</t>
         </is>
       </c>
-      <c r="F5" s="1" t="inlineStr">
+      <c r="J5" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pelnas</t>
+        </is>
+      </c>
+      <c r="K5" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Marža</t>
         </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>34942</v>
+      </c>
+      <c r="B6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
+        </is>
+      </c>
+      <c r="C6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">800 g</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>48.12</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="K6" s="4" t="n">
+        <v>0.12033</v>
       </c>
     </row>
   </sheetData>
@@ -785,21 +1374,177 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="24" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PILTUVĖLIS (iš sutikusių su statistika)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Laikotarpis</t>
+        </is>
+      </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-07-18 – 2026-08-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sugeneruota</t>
+        </is>
+      </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-16 12:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Žingsnis</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sesijos</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Perėjimas</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nuo pradžios</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Atidarė dėžę</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prisidėjo bent vieną</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pasiekė minimumą</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>0.666667</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Įsidėjo į krepšelį</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nupirko</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:N59"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
     <col min="5" max="5" width="30" customWidth="1"/>
-    <col min="6" max="6" width="20" customWidth="1"/>
-    <col min="7" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="40" customWidth="1"/>
-    <col min="9" max="9" width="10" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
-    <col min="11" max="11" width="12" customWidth="1"/>
-    <col min="12" max="12" width="13" customWidth="1"/>
+    <col min="6" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="40" customWidth="1"/>
+    <col min="8" max="8" width="8" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="10" customWidth="1"/>
+    <col min="11" max="11" width="9" customWidth="1"/>
+    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="13" max="13" width="12" customWidth="1"/>
+    <col min="14" max="14" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -820,45 +1565,55 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rinkinio ID</t>
+          <t xml:space="preserve">Dėžės ID</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rinkinys</t>
+          <t xml:space="preserve">Dėžė</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kategorija</t>
+          <t xml:space="preserve">Prekės ID</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prekės ID</t>
+          <t xml:space="preserve">Prekė</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prekė</t>
+          <t xml:space="preserve">Dydis</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skirtukas</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Įrenginys</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Kiekis</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sesijos</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Suma EUR</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Savikaina EUR</t>
         </is>
@@ -872,161 +1627,3436 @@
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">parduotuve</t>
+          <t xml:space="preserve">pardavimai</t>
         </is>
       </c>
       <c r="C2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">pajamos</t>
-        </is>
-      </c>
-      <c r="D2" s="2"/>
+          <t xml:space="preserve">parduota</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>34942</v>
+      </c>
       <c r="E2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F2" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Visa parduotuvė</t>
-        </is>
-      </c>
-      <c r="G2" s="2"/>
+          <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
+        </is>
+      </c>
+      <c r="F2" s="2"/>
+      <c r="G2" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
       <c r="H2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">800</t>
         </is>
       </c>
       <c r="I2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K2" s="3" t="n">
-        <v>62.22</v>
-      </c>
-      <c r="L2" s="3" t="n">
+          <t xml:space="preserve">be_vistienos</t>
+        </is>
+      </c>
+      <c r="J2" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" s="3" t="n">
+        <v>48.12</v>
+      </c>
+      <c r="N2" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-06</t>
+          <t xml:space="preserve">2026-08-15</t>
         </is>
       </c>
       <c r="B3" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">parduotuve</t>
+          <t xml:space="preserve">pardavimai</t>
         </is>
       </c>
       <c r="C3" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">pajamos</t>
-        </is>
-      </c>
-      <c r="D3" s="2"/>
+          <t xml:space="preserve">parduota</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>34942</v>
+      </c>
       <c r="E3" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F3" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Visa parduotuvė</t>
-        </is>
-      </c>
-      <c r="G3" s="2"/>
+          <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>19471</v>
+      </c>
+      <c r="G3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Animonda GranCarno Adult: konservai šunims su širdimis, 800 g</t>
+        </is>
+      </c>
       <c r="H3" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">800</t>
         </is>
       </c>
       <c r="I3" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" s="3" t="n">
-        <v>8.8</v>
-      </c>
-      <c r="L3" s="3" t="n">
-        <v>0</v>
+          <t xml:space="preserve">be_vistienos</t>
+        </is>
+      </c>
+      <c r="J3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="3" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>2.01</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-05</t>
+          <t xml:space="preserve">2026-08-15</t>
         </is>
       </c>
       <c r="B4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">parduotuve</t>
+          <t xml:space="preserve">pardavimai</t>
         </is>
       </c>
       <c r="C4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">pajamos</t>
-        </is>
-      </c>
-      <c r="D4" s="2"/>
+          <t xml:space="preserve">be_sav_suma</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>34942</v>
+      </c>
       <c r="E4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F4" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Visa parduotuvė</t>
-        </is>
-      </c>
-      <c r="G4" s="2"/>
+          <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>19538</v>
+      </c>
+      <c r="G4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Animonda GranCarno Adult Rumen: konservai suaugusiems šunims su galvijų prieskrandžiais, 800 g</t>
+        </is>
+      </c>
       <c r="H4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">800</t>
         </is>
       </c>
       <c r="I4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J4" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="K4" s="3" t="n">
-        <v>167.74</v>
-      </c>
-      <c r="L4" s="3" t="n">
+          <t xml:space="preserve">be_vistienos</t>
+        </is>
+      </c>
+      <c r="J4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="N4" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
-        </is>
+          <t xml:space="preserve">2026-08-15</t>
+        </is>
+      </c>
+      <c r="B5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pardavimai</t>
+        </is>
+      </c>
+      <c r="C5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">be_savikainos</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>34942</v>
+      </c>
+      <c r="E5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>19538</v>
+      </c>
+      <c r="G5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Animonda GranCarno Adult Rumen: konservai suaugusiems šunims su galvijų prieskrandžiais, 800 g</t>
+        </is>
+      </c>
+      <c r="H5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">800</t>
+        </is>
+      </c>
+      <c r="I5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">be_vistienos</t>
+        </is>
+      </c>
+      <c r="J5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Praleista 16 eilutės — jos priklauso SURENKAMOMS dėžėms.</t>
-        </is>
+          <t xml:space="preserve">2026-08-15</t>
+        </is>
+      </c>
+      <c r="B6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pardavimai</t>
+        </is>
+      </c>
+      <c r="C6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parduota</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>34942</v>
+      </c>
+      <c r="E6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>19538</v>
+      </c>
+      <c r="G6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Animonda GranCarno Adult Rumen: konservai suaugusiems šunims su galvijų prieskrandžiais, 800 g</t>
+        </is>
+      </c>
+      <c r="H6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">800</t>
+        </is>
+      </c>
+      <c r="I6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">be_vistienos</t>
+        </is>
+      </c>
+      <c r="J6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jas rasi lange „Surenkami rinkiniai" ir jo Excel faile.</t>
-        </is>
+          <t xml:space="preserve">2026-08-15</t>
+        </is>
+      </c>
+      <c r="B7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pardavimai</t>
+        </is>
+      </c>
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parduota</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>34942</v>
+      </c>
+      <c r="E7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>19479</v>
+      </c>
+      <c r="G7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Animonda GranCarno Adult: konservai šunims su lašiša, praturtinta špinatais, 800 g</t>
+        </is>
+      </c>
+      <c r="H7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">800</t>
+        </is>
+      </c>
+      <c r="I7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">be_vistienos</t>
+        </is>
+      </c>
+      <c r="J7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>2.01</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-15</t>
+        </is>
+      </c>
+      <c r="B8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pardavimai</t>
+        </is>
+      </c>
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parduota</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>34942</v>
+      </c>
+      <c r="E8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>19488</v>
+      </c>
+      <c r="G8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Animonda GranCarno Adult: konservai šunims su elniena, pagardinta obuoliais, 800 g</t>
+        </is>
+      </c>
+      <c r="H8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">800</t>
+        </is>
+      </c>
+      <c r="I8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">be_vistienos</t>
+        </is>
+      </c>
+      <c r="J8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>2.01</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-15</t>
+        </is>
+      </c>
+      <c r="B9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pardavimai</t>
+        </is>
+      </c>
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parduota</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>34942</v>
+      </c>
+      <c r="E9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>19496</v>
+      </c>
+      <c r="G9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Animonda GranCarno Adult: konservai suaugusiems šunims su žvėriena, 800 g</t>
+        </is>
+      </c>
+      <c r="H9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">800</t>
+        </is>
+      </c>
+      <c r="I9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">be_vistienos</t>
+        </is>
+      </c>
+      <c r="J9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="3" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>2.01</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-15</t>
+        </is>
+      </c>
+      <c r="B10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pardavimai</t>
+        </is>
+      </c>
+      <c r="C10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parduota</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>34942</v>
+      </c>
+      <c r="E10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>19504</v>
+      </c>
+      <c r="G10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Animonda GranCarno Adult: konservai suaugusiems šunims su kalakutiena, 800 g</t>
+        </is>
+      </c>
+      <c r="H10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">800</t>
+        </is>
+      </c>
+      <c r="I10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">be_vistienos</t>
+        </is>
+      </c>
+      <c r="J10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>2.01</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-15</t>
+        </is>
+      </c>
+      <c r="B11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pardavimai</t>
+        </is>
+      </c>
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parduota</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>34942</v>
+      </c>
+      <c r="E11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>19578</v>
+      </c>
+      <c r="G11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Animonda GranCarno Adult Beef + Rabbit with Herbs: konservai suaugusiems šunims su šviežia jautiena ir triušiena, paskaninta žolelėmis, 800 g</t>
+        </is>
+      </c>
+      <c r="H11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">800</t>
+        </is>
+      </c>
+      <c r="I11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">be_vistienos</t>
+        </is>
+      </c>
+      <c r="J11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="3" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="N11" s="3" t="n">
+        <v>2.01</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-15</t>
+        </is>
+      </c>
+      <c r="B12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pardavimai</t>
+        </is>
+      </c>
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parduota</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>34942</v>
+      </c>
+      <c r="E12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>19590</v>
+      </c>
+      <c r="G12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Animonda GranCarno Adult Beef + Duck Hearts: konservai suaugusiems šunims su jautiena ir ančių širdelėmis, 800 g</t>
+        </is>
+      </c>
+      <c r="H12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">800</t>
+        </is>
+      </c>
+      <c r="I12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">be_vistienos</t>
+        </is>
+      </c>
+      <c r="J12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="3" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="N12" s="3" t="n">
+        <v>2.01</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-15</t>
+        </is>
+      </c>
+      <c r="B13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pardavimai</t>
+        </is>
+      </c>
+      <c r="C13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parduota</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>34942</v>
+      </c>
+      <c r="E13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>19582</v>
+      </c>
+      <c r="G13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Animonda GranCarno Adult Beef + Lamb: konserv</t>
+        </is>
+      </c>
+      <c r="H13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">800</t>
+        </is>
+      </c>
+      <c r="I13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">be_vistienos</t>
+        </is>
+      </c>
+      <c r="J13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="N13" s="3" t="n">
+        <v>2.01</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-15</t>
+        </is>
+      </c>
+      <c r="B14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pardavimai</t>
+        </is>
+      </c>
+      <c r="C14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parduota</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>34942</v>
+      </c>
+      <c r="E14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>19562</v>
+      </c>
+      <c r="G14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Animonda GranCarno Adult Duck: konservai suaugusiems šunims su šviežia antiena, 800 g</t>
+        </is>
+      </c>
+      <c r="H14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">800</t>
+        </is>
+      </c>
+      <c r="I14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">be_vistienos</t>
+        </is>
+      </c>
+      <c r="J14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v>2.01</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-15</t>
+        </is>
+      </c>
+      <c r="B15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pardavimai</t>
+        </is>
+      </c>
+      <c r="C15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parduota</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>34942</v>
+      </c>
+      <c r="E15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>19570</v>
+      </c>
+      <c r="G15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Animonda GranCarno Adult Beef: konservai šunims su šviežia jautiena, 800 g</t>
+        </is>
+      </c>
+      <c r="H15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">800</t>
+        </is>
+      </c>
+      <c r="I15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">be_vistienos</t>
+        </is>
+      </c>
+      <c r="J15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="L15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="3" t="n">
+        <v>19.61</v>
+      </c>
+      <c r="N15" s="3" t="n">
+        <v>14.07</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-15</t>
+        </is>
+      </c>
+      <c r="B16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parduotuve</t>
+        </is>
+      </c>
+      <c r="C16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pajamos</t>
+        </is>
+      </c>
+      <c r="D16" s="2"/>
+      <c r="E16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F16" s="2"/>
+      <c r="G16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="3" t="n">
+        <v>62.22</v>
+      </c>
+      <c r="N16" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-06</t>
+        </is>
+      </c>
+      <c r="B17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parduotuve</t>
+        </is>
+      </c>
+      <c r="C17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pajamos</t>
+        </is>
+      </c>
+      <c r="D17" s="2"/>
+      <c r="E17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F17" s="2"/>
+      <c r="G17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="3" t="n">
+        <v>8.8</v>
+      </c>
+      <c r="N17" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-05</t>
+        </is>
+      </c>
+      <c r="B18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parduotuve</t>
+        </is>
+      </c>
+      <c r="C18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pajamos</t>
+        </is>
+      </c>
+      <c r="D18" s="2"/>
+      <c r="E18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F18" s="2"/>
+      <c r="G18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K18" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="L18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="3" t="n">
+        <v>167.74</v>
+      </c>
+      <c r="N18" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-15</t>
+        </is>
+      </c>
+      <c r="B19" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pardavimai</t>
+        </is>
+      </c>
+      <c r="C19" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parduota_sd</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>34942</v>
+      </c>
+      <c r="E19" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
+        </is>
+      </c>
+      <c r="F19" s="2"/>
+      <c r="G19" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H19" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">800</t>
+        </is>
+      </c>
+      <c r="I19" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">be_vistienos</t>
+        </is>
+      </c>
+      <c r="J19" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="3" t="n">
+        <v>48.12</v>
+      </c>
+      <c r="N19" s="3" t="n">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-15</t>
+        </is>
+      </c>
+      <c r="B20" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pardavimai</t>
+        </is>
+      </c>
+      <c r="C20" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dovana</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>34942</v>
+      </c>
+      <c r="E20" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>16305</v>
+      </c>
+      <c r="G20" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ruda kiaulės ausis, 1 vnt.</t>
+        </is>
+      </c>
+      <c r="H20" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">800</t>
+        </is>
+      </c>
+      <c r="I20" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">be_vistienos</t>
+        </is>
+      </c>
+      <c r="J20" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-16</t>
+        </is>
+      </c>
+      <c r="B21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">laukai</t>
+        </is>
+      </c>
+      <c r="C21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">atidare</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>34942</v>
+      </c>
+      <c r="E21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
+        </is>
+      </c>
+      <c r="F21" s="2"/>
+      <c r="G21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">800</t>
+        </is>
+      </c>
+      <c r="I21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">be_vistienos</t>
+        </is>
+      </c>
+      <c r="J21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">desktop</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="L21" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-16</t>
+        </is>
+      </c>
+      <c r="B22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">laukai</t>
+        </is>
+      </c>
+      <c r="C22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dovana_atrakinta</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>34942</v>
+      </c>
+      <c r="E22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
+        </is>
+      </c>
+      <c r="F22" s="2"/>
+      <c r="G22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">800</t>
+        </is>
+      </c>
+      <c r="I22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">be_vistienos</t>
+        </is>
+      </c>
+      <c r="J22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">desktop</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L22" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-16</t>
+        </is>
+      </c>
+      <c r="B23" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">laukai</t>
+        </is>
+      </c>
+      <c r="C23" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dovana_rinko</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>34942</v>
+      </c>
+      <c r="E23" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
+        </is>
+      </c>
+      <c r="F23" s="2"/>
+      <c r="G23" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H23" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">800</t>
+        </is>
+      </c>
+      <c r="I23" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">be_vistienos</t>
+        </is>
+      </c>
+      <c r="J23" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">desktop</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-16</t>
+        </is>
+      </c>
+      <c r="B24" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">laukai</t>
+        </is>
+      </c>
+      <c r="C24" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dovana_rinko</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>34942</v>
+      </c>
+      <c r="E24" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>17386</v>
+      </c>
+      <c r="G24" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Natūralios triušio ausys su kailiuku, 100 g</t>
+        </is>
+      </c>
+      <c r="H24" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">800</t>
+        </is>
+      </c>
+      <c r="I24" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">be_vistienos</t>
+        </is>
+      </c>
+      <c r="J24" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">desktop</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-16</t>
+        </is>
+      </c>
+      <c r="B25" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">laukai</t>
+        </is>
+      </c>
+      <c r="C25" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dydis_perjunge</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>34942</v>
+      </c>
+      <c r="E25" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
+        </is>
+      </c>
+      <c r="F25" s="2"/>
+      <c r="G25" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H25" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">800</t>
+        </is>
+      </c>
+      <c r="I25" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">be_vistienos</t>
+        </is>
+      </c>
+      <c r="J25" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">desktop</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-16</t>
+        </is>
+      </c>
+      <c r="B26" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">laukai</t>
+        </is>
+      </c>
+      <c r="C26" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">idejo</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>34942</v>
+      </c>
+      <c r="E26" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>19471</v>
+      </c>
+      <c r="G26" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Animonda GranCarno Adult: konservai šunims su širdimis, 800 g</t>
+        </is>
+      </c>
+      <c r="H26" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">800</t>
+        </is>
+      </c>
+      <c r="I26" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">be_vistienos</t>
+        </is>
+      </c>
+      <c r="J26" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">desktop</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L26" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-16</t>
+        </is>
+      </c>
+      <c r="B27" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">laukai</t>
+        </is>
+      </c>
+      <c r="C27" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">idejo</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>34942</v>
+      </c>
+      <c r="E27" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>19479</v>
+      </c>
+      <c r="G27" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Animonda GranCarno Adult: konservai šunims su lašiša, praturtinta špinatais, 800 g</t>
+        </is>
+      </c>
+      <c r="H27" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">800</t>
+        </is>
+      </c>
+      <c r="I27" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">be_vistienos</t>
+        </is>
+      </c>
+      <c r="J27" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">desktop</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L27" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-16</t>
+        </is>
+      </c>
+      <c r="B28" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">laukai</t>
+        </is>
+      </c>
+      <c r="C28" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">idejo</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>34942</v>
+      </c>
+      <c r="E28" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>19488</v>
+      </c>
+      <c r="G28" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Animonda GranCarno Adult: konservai šunims su elniena, pagardinta obuoliais, 800 g</t>
+        </is>
+      </c>
+      <c r="H28" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">800</t>
+        </is>
+      </c>
+      <c r="I28" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">be_vistienos</t>
+        </is>
+      </c>
+      <c r="J28" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">desktop</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L28" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-16</t>
+        </is>
+      </c>
+      <c r="B29" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">laukai</t>
+        </is>
+      </c>
+      <c r="C29" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">idejo</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>34942</v>
+      </c>
+      <c r="E29" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>19496</v>
+      </c>
+      <c r="G29" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Animonda GranCarno Adult: konservai suaugusiems šunims su žvėriena, 800 g</t>
+        </is>
+      </c>
+      <c r="H29" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">800</t>
+        </is>
+      </c>
+      <c r="I29" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">be_vistienos</t>
+        </is>
+      </c>
+      <c r="J29" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">desktop</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L29" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-16</t>
+        </is>
+      </c>
+      <c r="B30" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">laukai</t>
+        </is>
+      </c>
+      <c r="C30" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">idejo</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>34942</v>
+      </c>
+      <c r="E30" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>19504</v>
+      </c>
+      <c r="G30" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Animonda GranCarno Adult: konservai suaugusiems šunims su kalakutiena, 800 g</t>
+        </is>
+      </c>
+      <c r="H30" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">800</t>
+        </is>
+      </c>
+      <c r="I30" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">be_vistienos</t>
+        </is>
+      </c>
+      <c r="J30" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">desktop</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L30" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-16</t>
+        </is>
+      </c>
+      <c r="B31" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">laukai</t>
+        </is>
+      </c>
+      <c r="C31" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">idejo</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>34942</v>
+      </c>
+      <c r="E31" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>19538</v>
+      </c>
+      <c r="G31" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Animonda GranCarno Adult Rumen: konservai suaugusiems šunims su galvijų prieskrandžiais, 800 g</t>
+        </is>
+      </c>
+      <c r="H31" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">800</t>
+        </is>
+      </c>
+      <c r="I31" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">be_vistienos</t>
+        </is>
+      </c>
+      <c r="J31" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">desktop</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L31" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-16</t>
+        </is>
+      </c>
+      <c r="B32" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">laukai</t>
+        </is>
+      </c>
+      <c r="C32" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">idejo</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>34942</v>
+      </c>
+      <c r="E32" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>19562</v>
+      </c>
+      <c r="G32" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Animonda GranCarno Adult Duck: konservai suaugusiems šunims su šviežia antiena, 800 g</t>
+        </is>
+      </c>
+      <c r="H32" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">800</t>
+        </is>
+      </c>
+      <c r="I32" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">be_vistienos</t>
+        </is>
+      </c>
+      <c r="J32" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">desktop</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L32" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-16</t>
+        </is>
+      </c>
+      <c r="B33" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">laukai</t>
+        </is>
+      </c>
+      <c r="C33" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">idejo</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>34942</v>
+      </c>
+      <c r="E33" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>19570</v>
+      </c>
+      <c r="G33" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Animonda GranCarno Adult Beef: konservai šunims su šviežia jautiena, 800 g</t>
+        </is>
+      </c>
+      <c r="H33" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">800</t>
+        </is>
+      </c>
+      <c r="I33" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">be_vistienos</t>
+        </is>
+      </c>
+      <c r="J33" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">desktop</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="L33" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-16</t>
+        </is>
+      </c>
+      <c r="B34" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">laukai</t>
+        </is>
+      </c>
+      <c r="C34" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">idejo</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>34942</v>
+      </c>
+      <c r="E34" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>19578</v>
+      </c>
+      <c r="G34" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Animonda GranCarno Adult Beef + Rabbit with Herbs: konservai suaugusiems šunims su šviežia jautiena ir triušiena, paskaninta žolelėmis, 800 g</t>
+        </is>
+      </c>
+      <c r="H34" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">800</t>
+        </is>
+      </c>
+      <c r="I34" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">be_vistienos</t>
+        </is>
+      </c>
+      <c r="J34" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">desktop</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L34" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-16</t>
+        </is>
+      </c>
+      <c r="B35" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">laukai</t>
+        </is>
+      </c>
+      <c r="C35" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">idejo</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>34942</v>
+      </c>
+      <c r="E35" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>19582</v>
+      </c>
+      <c r="G35" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Animonda GranCarno Adult Beef + Lamb: konserv</t>
+        </is>
+      </c>
+      <c r="H35" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">800</t>
+        </is>
+      </c>
+      <c r="I35" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">be_vistienos</t>
+        </is>
+      </c>
+      <c r="J35" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">desktop</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L35" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-16</t>
+        </is>
+      </c>
+      <c r="B36" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">laukai</t>
+        </is>
+      </c>
+      <c r="C36" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">idejo</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>34942</v>
+      </c>
+      <c r="E36" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>19590</v>
+      </c>
+      <c r="G36" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Animonda GranCarno Adult Beef + Duck Hearts: konservai suaugusiems šunims su jautiena ir ančių širdelėmis, 800 g</t>
+        </is>
+      </c>
+      <c r="H36" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">800</t>
+        </is>
+      </c>
+      <c r="I36" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">be_vistienos</t>
+        </is>
+      </c>
+      <c r="J36" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">desktop</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L36" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-16</t>
+        </is>
+      </c>
+      <c r="B37" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">laukai</t>
+        </is>
+      </c>
+      <c r="C37" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">iseme</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>34942</v>
+      </c>
+      <c r="E37" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>19570</v>
+      </c>
+      <c r="G37" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Animonda GranCarno Adult Beef: konservai šunims su šviežia jautiena, 800 g</t>
+        </is>
+      </c>
+      <c r="H37" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">800</t>
+        </is>
+      </c>
+      <c r="I37" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">be_vistienos</t>
+        </is>
+      </c>
+      <c r="J37" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">desktop</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-16</t>
+        </is>
+      </c>
+      <c r="B38" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">laukai</t>
+        </is>
+      </c>
+      <c r="C38" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">krepselis</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>34942</v>
+      </c>
+      <c r="E38" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
+        </is>
+      </c>
+      <c r="F38" s="2"/>
+      <c r="G38" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H38" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">800</t>
+        </is>
+      </c>
+      <c r="I38" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">be_vistienos</t>
+        </is>
+      </c>
+      <c r="J38" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">desktop</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-16</t>
+        </is>
+      </c>
+      <c r="B39" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">laukai</t>
+        </is>
+      </c>
+      <c r="C39" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">min_pasiekta</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>34942</v>
+      </c>
+      <c r="E39" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
+        </is>
+      </c>
+      <c r="F39" s="2"/>
+      <c r="G39" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H39" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">800</t>
+        </is>
+      </c>
+      <c r="I39" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">be_vistienos</t>
+        </is>
+      </c>
+      <c r="J39" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">desktop</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L39" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-16</t>
+        </is>
+      </c>
+      <c r="B40" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">laukai</t>
+        </is>
+      </c>
+      <c r="C40" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rodyta</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>34942</v>
+      </c>
+      <c r="E40" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>19471</v>
+      </c>
+      <c r="G40" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Animonda GranCarno Adult: konservai šunims su širdimis, 800 g</t>
+        </is>
+      </c>
+      <c r="H40" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">800</t>
+        </is>
+      </c>
+      <c r="I40" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">be_vistienos</t>
+        </is>
+      </c>
+      <c r="J40" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">desktop</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L40" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-16</t>
+        </is>
+      </c>
+      <c r="B41" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">laukai</t>
+        </is>
+      </c>
+      <c r="C41" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rodyta</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>34942</v>
+      </c>
+      <c r="E41" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>19479</v>
+      </c>
+      <c r="G41" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Animonda GranCarno Adult: konservai šunims su lašiša, praturtinta špinatais, 800 g</t>
+        </is>
+      </c>
+      <c r="H41" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">800</t>
+        </is>
+      </c>
+      <c r="I41" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">be_vistienos</t>
+        </is>
+      </c>
+      <c r="J41" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">desktop</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L41" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-16</t>
+        </is>
+      </c>
+      <c r="B42" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">laukai</t>
+        </is>
+      </c>
+      <c r="C42" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rodyta</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>34942</v>
+      </c>
+      <c r="E42" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>19488</v>
+      </c>
+      <c r="G42" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Animonda GranCarno Adult: konservai šunims su elniena, pagardinta obuoliais, 800 g</t>
+        </is>
+      </c>
+      <c r="H42" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">800</t>
+        </is>
+      </c>
+      <c r="I42" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">be_vistienos</t>
+        </is>
+      </c>
+      <c r="J42" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">desktop</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="L42" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-16</t>
+        </is>
+      </c>
+      <c r="B43" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">laukai</t>
+        </is>
+      </c>
+      <c r="C43" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rodyta</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>34942</v>
+      </c>
+      <c r="E43" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>19496</v>
+      </c>
+      <c r="G43" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Animonda GranCarno Adult: konservai suaugusiems šunims su žvėriena, 800 g</t>
+        </is>
+      </c>
+      <c r="H43" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">800</t>
+        </is>
+      </c>
+      <c r="I43" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">be_vistienos</t>
+        </is>
+      </c>
+      <c r="J43" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">desktop</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="L43" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-16</t>
+        </is>
+      </c>
+      <c r="B44" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">laukai</t>
+        </is>
+      </c>
+      <c r="C44" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rodyta</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>34942</v>
+      </c>
+      <c r="E44" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>19504</v>
+      </c>
+      <c r="G44" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Animonda GranCarno Adult: konservai suaugusiems šunims su kalakutiena, 800 g</t>
+        </is>
+      </c>
+      <c r="H44" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">800</t>
+        </is>
+      </c>
+      <c r="I44" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">be_vistienos</t>
+        </is>
+      </c>
+      <c r="J44" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">desktop</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="L44" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-16</t>
+        </is>
+      </c>
+      <c r="B45" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">laukai</t>
+        </is>
+      </c>
+      <c r="C45" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rodyta</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>34942</v>
+      </c>
+      <c r="E45" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>19538</v>
+      </c>
+      <c r="G45" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Animonda GranCarno Adult Rumen: konservai suaugusiems šunims su galvijų prieskrandžiais, 800 g</t>
+        </is>
+      </c>
+      <c r="H45" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">800</t>
+        </is>
+      </c>
+      <c r="I45" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">be_vistienos</t>
+        </is>
+      </c>
+      <c r="J45" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">desktop</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L45" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-16</t>
+        </is>
+      </c>
+      <c r="B46" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">laukai</t>
+        </is>
+      </c>
+      <c r="C46" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rodyta</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>34942</v>
+      </c>
+      <c r="E46" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>19562</v>
+      </c>
+      <c r="G46" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Animonda GranCarno Adult Duck: konservai suaugusiems šunims su šviežia antiena, 800 g</t>
+        </is>
+      </c>
+      <c r="H46" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">800</t>
+        </is>
+      </c>
+      <c r="I46" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">be_vistienos</t>
+        </is>
+      </c>
+      <c r="J46" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">desktop</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="L46" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-16</t>
+        </is>
+      </c>
+      <c r="B47" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">laukai</t>
+        </is>
+      </c>
+      <c r="C47" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rodyta</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>34942</v>
+      </c>
+      <c r="E47" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="n">
+        <v>19570</v>
+      </c>
+      <c r="G47" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Animonda GranCarno Adult Beef: konservai šunims su šviežia jautiena, 800 g</t>
+        </is>
+      </c>
+      <c r="H47" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">800</t>
+        </is>
+      </c>
+      <c r="I47" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">be_vistienos</t>
+        </is>
+      </c>
+      <c r="J47" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">desktop</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="L47" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-16</t>
+        </is>
+      </c>
+      <c r="B48" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">laukai</t>
+        </is>
+      </c>
+      <c r="C48" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rodyta</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>34942</v>
+      </c>
+      <c r="E48" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>19578</v>
+      </c>
+      <c r="G48" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Animonda GranCarno Adult Beef + Rabbit with Herbs: konservai suaugusiems šunims su šviežia jautiena ir triušiena, paskaninta žolelėmis, 800 g</t>
+        </is>
+      </c>
+      <c r="H48" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">800</t>
+        </is>
+      </c>
+      <c r="I48" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">be_vistienos</t>
+        </is>
+      </c>
+      <c r="J48" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">desktop</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="L48" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-16</t>
+        </is>
+      </c>
+      <c r="B49" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">laukai</t>
+        </is>
+      </c>
+      <c r="C49" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rodyta</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>34942</v>
+      </c>
+      <c r="E49" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="n">
+        <v>19582</v>
+      </c>
+      <c r="G49" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Animonda GranCarno Adult Beef + Lamb: konserv</t>
+        </is>
+      </c>
+      <c r="H49" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">800</t>
+        </is>
+      </c>
+      <c r="I49" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">be_vistienos</t>
+        </is>
+      </c>
+      <c r="J49" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">desktop</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="L49" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-16</t>
+        </is>
+      </c>
+      <c r="B50" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">laukai</t>
+        </is>
+      </c>
+      <c r="C50" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rodyta</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>34942</v>
+      </c>
+      <c r="E50" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>19590</v>
+      </c>
+      <c r="G50" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Animonda GranCarno Adult Beef + Duck Hearts: konservai suaugusiems šunims su jautiena ir ančių širdelėmis, 800 g</t>
+        </is>
+      </c>
+      <c r="H50" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">800</t>
+        </is>
+      </c>
+      <c r="I50" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">be_vistienos</t>
+        </is>
+      </c>
+      <c r="J50" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">desktop</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="L50" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-16</t>
+        </is>
+      </c>
+      <c r="B51" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">laukai</t>
+        </is>
+      </c>
+      <c r="C51" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">iseme_p1</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>34942</v>
+      </c>
+      <c r="E51" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="n">
+        <v>19570</v>
+      </c>
+      <c r="G51" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Animonda GranCarno Adult Beef: konservai šunims su šviežia jautiena, 800 g</t>
+        </is>
+      </c>
+      <c r="H51" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">800</t>
+        </is>
+      </c>
+      <c r="I51" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">be_vistienos</t>
+        </is>
+      </c>
+      <c r="J51" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K51" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-16</t>
+        </is>
+      </c>
+      <c r="B52" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">piltuvelis</t>
+        </is>
+      </c>
+      <c r="C52" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">atidare</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>34942</v>
+      </c>
+      <c r="E52" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
+        </is>
+      </c>
+      <c r="F52" s="2"/>
+      <c r="G52" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H52" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">800</t>
+        </is>
+      </c>
+      <c r="I52" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">be_vistienos</t>
+        </is>
+      </c>
+      <c r="J52" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">desktop</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-16</t>
+        </is>
+      </c>
+      <c r="B53" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">piltuvelis</t>
+        </is>
+      </c>
+      <c r="C53" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">idejo</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>34942</v>
+      </c>
+      <c r="E53" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
+        </is>
+      </c>
+      <c r="F53" s="2"/>
+      <c r="G53" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H53" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">800</t>
+        </is>
+      </c>
+      <c r="I53" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">be_vistienos</t>
+        </is>
+      </c>
+      <c r="J53" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">desktop</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-16</t>
+        </is>
+      </c>
+      <c r="B54" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">piltuvelis</t>
+        </is>
+      </c>
+      <c r="C54" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">krepselis</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>34942</v>
+      </c>
+      <c r="E54" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
+        </is>
+      </c>
+      <c r="F54" s="2"/>
+      <c r="G54" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H54" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">800</t>
+        </is>
+      </c>
+      <c r="I54" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">be_vistienos</t>
+        </is>
+      </c>
+      <c r="J54" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">desktop</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-16</t>
+        </is>
+      </c>
+      <c r="B55" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">piltuvelis</t>
+        </is>
+      </c>
+      <c r="C55" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">min_pasiekta</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>34942</v>
+      </c>
+      <c r="E55" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
+        </is>
+      </c>
+      <c r="F55" s="2"/>
+      <c r="G55" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H55" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">800</t>
+        </is>
+      </c>
+      <c r="I55" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">be_vistienos</t>
+        </is>
+      </c>
+      <c r="J55" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">desktop</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-16</t>
+        </is>
+      </c>
+      <c r="B56" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">laukai</t>
+        </is>
+      </c>
+      <c r="C56" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kabliukas</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v>34942</v>
+      </c>
+      <c r="E56" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="n">
+        <v>19570</v>
+      </c>
+      <c r="G56" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Animonda GranCarno Adult Beef: konservai šunims su šviežia jautiena, 800 g</t>
+        </is>
+      </c>
+      <c r="H56" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">800</t>
+        </is>
+      </c>
+      <c r="I56" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">be_vistienos</t>
+        </is>
+      </c>
+      <c r="J56" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K56" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L56" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-16</t>
+        </is>
+      </c>
+      <c r="B57" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">laukai</t>
+        </is>
+      </c>
+      <c r="C57" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">riba_pasieke</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="n">
+        <v>34942</v>
+      </c>
+      <c r="E57" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
+        </is>
+      </c>
+      <c r="F57" s="2"/>
+      <c r="G57" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H57" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">800</t>
+        </is>
+      </c>
+      <c r="I57" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">be_vistienos</t>
+        </is>
+      </c>
+      <c r="J57" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K57" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L57" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-16</t>
+        </is>
+      </c>
+      <c r="B58" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">laukai</t>
+        </is>
+      </c>
+      <c r="C58" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">uzdarytoja</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>34942</v>
+      </c>
+      <c r="E58" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="n">
+        <v>19570</v>
+      </c>
+      <c r="G58" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Animonda GranCarno Adult Beef: konservai šunims su šviežia jautiena, 800 g</t>
+        </is>
+      </c>
+      <c r="H58" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">800</t>
+        </is>
+      </c>
+      <c r="I58" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">be_vistienos</t>
+        </is>
+      </c>
+      <c r="J58" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K58" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L58" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-16</t>
+        </is>
+      </c>
+      <c r="B59" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">laukai</t>
+        </is>
+      </c>
+      <c r="C59" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">riba_pasieke_krepselis</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>34942</v>
+      </c>
+      <c r="E59" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TEST Konservu deze 800 Be vistienos</t>
+        </is>
+      </c>
+      <c r="F59" s="2"/>
+      <c r="G59" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H59" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">800</t>
+        </is>
+      </c>
+      <c r="I59" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">be_vistienos</t>
+        </is>
+      </c>
+      <c r="J59" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K59" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L59" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
